--- a/data/ARFYE (TRY).xlsx
+++ b/data/ARFYE (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
+        <v>121903505</v>
+      </c>
+      <c r="C3">
         <v>256454481</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>542134587</v>
       </c>
-      <c r="D3">
-        <v>7455371.958369219</v>
-      </c>
       <c r="E3">
-        <v>1610458.8547897332</v>
+        <v>7978247.124889376</v>
       </c>
       <c r="F3">
-        <v>22577981.46839826</v>
+        <v>1723406.7997848527</v>
       </c>
       <c r="G3">
-        <v>39002487.91584749</v>
+        <v>24161465.952592943</v>
+      </c>
+      <c r="H3">
+        <v>41737888.97666324</v>
       </c>
     </row>
     <row r="4">
@@ -475,12 +482,15 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
+        <v>593751129</v>
+      </c>
+      <c r="C5">
         <v>534129977</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0</v>
       </c>
     </row>
@@ -494,22 +504,25 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
+        <v>310757713</v>
+      </c>
+      <c r="C7">
         <v>342097907</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>160747512</v>
       </c>
-      <c r="D7">
-        <v>662267893.5343874</v>
-      </c>
       <c r="E7">
-        <v>739117575.4007918</v>
+        <v>708715399.7146816</v>
       </c>
       <c r="F7">
-        <v>618362264.4178165</v>
+        <v>790954858.2987733</v>
       </c>
       <c r="G7">
-        <v>246555833.89873546</v>
+        <v>661730492.5602486</v>
+      </c>
+      <c r="H7">
+        <v>263847784.37769145</v>
       </c>
     </row>
     <row r="8">
@@ -527,22 +540,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
+        <v>3213233</v>
+      </c>
+      <c r="C10">
         <v>3173330</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>320567</v>
       </c>
-      <c r="D10">
-        <v>198195.65994499915</v>
-      </c>
       <c r="E10">
-        <v>148994.94361487476</v>
+        <v>212095.9172730027</v>
       </c>
       <c r="F10">
-        <v>3513013.2494639494</v>
+        <v>159444.55718054454</v>
       </c>
       <c r="G10">
-        <v>378820.4487440678</v>
+        <v>3759394.97234217</v>
+      </c>
+      <c r="H10">
+        <v>405388.6476648393</v>
       </c>
     </row>
     <row r="11">
@@ -565,22 +581,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
+        <v>82614260</v>
+      </c>
+      <c r="C14">
         <v>49068354</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>26339012</v>
       </c>
-      <c r="D14">
-        <v>34406048.619347714</v>
-      </c>
       <c r="E14">
-        <v>18186269.029002212</v>
+        <v>36819082.93897638</v>
       </c>
       <c r="F14">
-        <v>26283042.123175792</v>
+        <v>19461745.08841534</v>
       </c>
       <c r="G14">
-        <v>7102850.973123229</v>
+        <v>28126377.385796</v>
+      </c>
+      <c r="H14">
+        <v>7601002.427682184</v>
       </c>
     </row>
     <row r="15">
@@ -598,22 +617,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
+        <v>24780954</v>
+      </c>
+      <c r="C17">
         <v>13330809</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>39029424</v>
       </c>
-      <c r="D17">
-        <v>10088050.227819983</v>
-      </c>
       <c r="E17">
-        <v>7458410.803478786</v>
+        <v>10795565.690789437</v>
       </c>
       <c r="F17">
-        <v>1039715.3327492708</v>
+        <v>7981499.096406528</v>
       </c>
       <c r="G17">
-        <v>1631198.3282232822</v>
+        <v>1112634.743179834</v>
+      </c>
+      <c r="H17">
+        <v>1745600.8157530548</v>
       </c>
     </row>
     <row r="18">
@@ -626,16 +648,19 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
+        <v>18454162</v>
+      </c>
+      <c r="C19">
         <v>9063455</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>2229268</v>
       </c>
-      <c r="D19">
-        <v>448858.18687819625</v>
-      </c>
       <c r="E19">
-        <v>36124.654788025735</v>
+        <v>480338.41355480195</v>
+      </c>
+      <c r="F19">
+        <v>38658.22185795149</v>
       </c>
     </row>
     <row r="20">
@@ -648,22 +673,25 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
+        <v>117117734</v>
+      </c>
+      <c r="C21">
         <v>104454606</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>139603</v>
       </c>
-      <c r="D21">
-        <v>437755.9594264705</v>
-      </c>
       <c r="E21">
-        <v>469467.55358052516</v>
+        <v>468457.5423197772</v>
       </c>
       <c r="F21">
-        <v>108345.47557332162</v>
+        <v>502393.19788438396</v>
       </c>
       <c r="G21">
-        <v>93447.9583276412</v>
+        <v>115944.17874982925</v>
+      </c>
+      <c r="H21">
+        <v>100001.83881065094</v>
       </c>
     </row>
     <row r="22">
@@ -681,22 +709,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
+        <v>1272592690</v>
+      </c>
+      <c r="C24">
         <v>1311772919</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>770939973</v>
       </c>
-      <c r="D24">
-        <v>715302174.146174</v>
-      </c>
       <c r="E24">
-        <v>767027301.2400459</v>
+        <v>765469187.3424844</v>
       </c>
       <c r="F24">
-        <v>671884362.067177</v>
+        <v>820822005.2603029</v>
       </c>
       <c r="G24">
-        <v>294764639.5230012</v>
+        <v>719006309.7929094</v>
+      </c>
+      <c r="H24">
+        <v>315437667.0842654</v>
       </c>
     </row>
     <row r="25">
@@ -718,8 +749,8 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
-      <c r="G28">
-        <v>47234442.77023776</v>
+      <c r="H28">
+        <v>50547183.87381876</v>
       </c>
     </row>
     <row r="29">
@@ -767,22 +798,25 @@
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
       <c r="B37">
+        <v>105282590</v>
+      </c>
+      <c r="C37">
         <v>92838843</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>87505014</v>
       </c>
-      <c r="D37">
-        <v>99224550.16274552</v>
-      </c>
       <c r="E37">
-        <v>80705592.99082778</v>
+        <v>106183566.22243275</v>
       </c>
       <c r="F37">
-        <v>44931834.13633204</v>
+        <v>86365800.23599623</v>
       </c>
       <c r="G37">
-        <v>7579096.10895635</v>
+        <v>48083084.052135</v>
+      </c>
+      <c r="H37">
+        <v>8110648.546872496</v>
       </c>
     </row>
     <row r="38">
@@ -795,22 +829,25 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
+        <v>1305768367</v>
+      </c>
+      <c r="C39">
         <v>1252851961</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>1209569993</v>
       </c>
-      <c r="D39">
-        <v>1355118556.0625677</v>
-      </c>
       <c r="E39">
-        <v>1125286493.7882504</v>
+        <v>1450158460.793325</v>
       </c>
       <c r="F39">
-        <v>992106336.791068</v>
+        <v>1204207353.2849934</v>
       </c>
       <c r="G39">
-        <v>460503883.7515458</v>
+        <v>1061686737.1992594</v>
+      </c>
+      <c r="H39">
+        <v>492800869.9038555</v>
       </c>
     </row>
     <row r="40">
@@ -818,19 +855,22 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
+        <v>4665939</v>
+      </c>
+      <c r="C40">
         <v>4932227</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>4610955</v>
       </c>
-      <c r="D40">
-        <v>1330611.3765420734</v>
-      </c>
       <c r="E40">
-        <v>1490107.896922766</v>
+        <v>1423932.4943840916</v>
       </c>
       <c r="F40">
-        <v>576684.2361473263</v>
+        <v>1594615.146069718</v>
+      </c>
+      <c r="G40">
+        <v>617129.4168423804</v>
       </c>
     </row>
     <row r="41">
@@ -838,42 +878,42 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
+        <v>1287389</v>
+      </c>
+      <c r="C41">
         <v>986170</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>945457</v>
       </c>
-      <c r="D41">
-        <v>1084333.2418731179</v>
-      </c>
       <c r="E41">
-        <v>833118.5236221033</v>
+        <v>1160381.8853980436</v>
       </c>
       <c r="F41">
-        <v>666269.1521551904</v>
+        <v>891548.470404426</v>
       </c>
       <c r="G41">
-        <v>210821.74505378323</v>
+        <v>712997.2826664133</v>
+      </c>
+      <c r="H41">
+        <v>225607.5204204062</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
       <c r="C42">
         <v>0</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0</v>
       </c>
-      <c r="F42">
-        <v>1358938.8224232453</v>
-      </c>
       <c r="G42">
-        <v>516557.8886975012</v>
+        <v>1454246.6577710991</v>
+      </c>
+      <c r="H42">
+        <v>552786.1672566688</v>
       </c>
     </row>
     <row r="43">
@@ -896,22 +936,25 @@
         <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
       <c r="B46">
+        <v>18453045</v>
+      </c>
+      <c r="C46">
         <v>16286346</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>18181930</v>
       </c>
-      <c r="D46">
-        <v>18009244.91652461</v>
-      </c>
       <c r="E46">
-        <v>18321543.910599995</v>
+        <v>19272305.56423103</v>
       </c>
       <c r="F46">
-        <v>15094402.640676878</v>
+        <v>19606507.340547606</v>
       </c>
       <c r="G46">
-        <v>13176553.710829705</v>
+        <v>16153033.697361624</v>
+      </c>
+      <c r="H46">
+        <v>14100678.322476704</v>
       </c>
     </row>
     <row r="47">
@@ -919,22 +962,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
+        <v>1435457330</v>
+      </c>
+      <c r="C47">
         <v>1367895547</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>1320813349</v>
       </c>
-      <c r="D47">
-        <v>1474767296.908601</v>
-      </c>
       <c r="E47">
-        <v>1226636857.1102233</v>
+        <v>1578198648.1886573</v>
       </c>
       <c r="F47">
-        <v>1054734465.7788028</v>
+        <v>1312665824.4780116</v>
       </c>
       <c r="G47">
-        <v>529221355.9753209</v>
+        <v>1128707228.306036</v>
+      </c>
+      <c r="H47">
+        <v>566337774.3347005</v>
       </c>
     </row>
     <row r="48">
@@ -942,22 +988,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
+        <v>2708050020</v>
+      </c>
+      <c r="C48">
         <v>2679668466</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>2091753322</v>
       </c>
-      <c r="D48">
-        <v>2190069471.054775</v>
-      </c>
       <c r="E48">
-        <v>1993664158.350269</v>
+        <v>2343667835.5311418</v>
       </c>
       <c r="F48">
-        <v>1726618827.8459797</v>
+        <v>2133487829.7383144</v>
       </c>
       <c r="G48">
-        <v>823985995.498322</v>
+        <v>1847713538.0989454</v>
+      </c>
+      <c r="H48">
+        <v>881775441.4189658</v>
       </c>
     </row>
     <row r="49">
@@ -970,22 +1019,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
+        <v>198828731</v>
+      </c>
+      <c r="C50">
         <v>209343466</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>242454757</v>
       </c>
-      <c r="D50">
-        <v>237757567.83473608</v>
-      </c>
       <c r="E50">
-        <v>155508078.6793877</v>
+        <v>254432460.59222746</v>
       </c>
       <c r="F50">
-        <v>76989767.39137924</v>
+        <v>166414484.55541328</v>
       </c>
       <c r="G50">
-        <v>52589812.5589121</v>
+        <v>82389368.86933435</v>
+      </c>
+      <c r="H50">
+        <v>56278147.24597443</v>
       </c>
     </row>
     <row r="51">
@@ -998,22 +1050,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
+        <v>14912064</v>
+      </c>
+      <c r="C52">
         <v>31030522</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>26791852</v>
       </c>
-      <c r="D52">
-        <v>31810970.705032635</v>
-      </c>
       <c r="E52">
-        <v>26263879.612444397</v>
+        <v>34042001.7920718</v>
       </c>
       <c r="F52">
-        <v>8199879.200978848</v>
+        <v>28105870.931255285</v>
       </c>
       <c r="G52">
-        <v>12410173.885858363</v>
+        <v>8774969.649396239</v>
+      </c>
+      <c r="H52">
+        <v>13280549.20359525</v>
       </c>
     </row>
     <row r="53">
@@ -1026,22 +1081,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
+        <v>1301355</v>
+      </c>
+      <c r="C54">
         <v>2245480</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>718158</v>
       </c>
-      <c r="D54">
-        <v>6662684.631464532</v>
-      </c>
       <c r="E54">
-        <v>1307857.0987828234</v>
+        <v>7129965.453347272</v>
       </c>
       <c r="F54">
-        <v>434668.0519360184</v>
+        <v>1399582.367773993</v>
       </c>
       <c r="G54">
-        <v>101188.97148983434</v>
+        <v>465153.06747999834</v>
+      </c>
+      <c r="H54">
+        <v>108285.76030375206</v>
       </c>
     </row>
     <row r="55">
@@ -1049,22 +1107,25 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
+        <v>40281986</v>
+      </c>
+      <c r="C55">
         <v>42017984</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>134457492</v>
       </c>
-      <c r="D55">
-        <v>34535383.59775126</v>
-      </c>
       <c r="E55">
-        <v>36264165.19406239</v>
+        <v>36957488.69865646</v>
       </c>
       <c r="F55">
-        <v>24407963.410688937</v>
+        <v>38807516.68885589</v>
       </c>
       <c r="G55">
-        <v>14917599.553673357</v>
+        <v>26119791.875324454</v>
+      </c>
+      <c r="H55">
+        <v>15963830.700055242</v>
       </c>
     </row>
     <row r="56">
@@ -1092,42 +1153,42 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
+        <v>754053</v>
+      </c>
+      <c r="C60">
         <v>1013333</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>756305</v>
       </c>
-      <c r="D60">
-        <v>644289.7734392169</v>
-      </c>
       <c r="E60">
-        <v>1961164.4599316423</v>
+        <v>689476.401880483</v>
       </c>
       <c r="F60">
-        <v>2393313.1891114926</v>
+        <v>2098708.796993059</v>
       </c>
       <c r="G60">
-        <v>4718215.849056492</v>
+        <v>2561165.851497675</v>
+      </c>
+      <c r="H60">
+        <v>5049123.268770678</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
       <c r="C61">
         <v>0</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>0</v>
       </c>
-      <c r="F61">
-        <v>35657925.81914458</v>
-      </c>
       <c r="G61">
-        <v>2929401.0304642995</v>
+        <v>38158759.31270604</v>
+      </c>
+      <c r="H61">
+        <v>3134851.6853962615</v>
       </c>
     </row>
     <row r="62">
@@ -1140,22 +1201,25 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
+        <v>3985861</v>
+      </c>
+      <c r="C63">
         <v>4302328</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>611345</v>
       </c>
-      <c r="D63">
-        <v>2962877.668307981</v>
-      </c>
       <c r="E63">
-        <v>969942.7994547322</v>
+        <v>3170676.174250569</v>
       </c>
       <c r="F63">
-        <v>2811179.762991429</v>
+        <v>1037968.7820095792</v>
       </c>
       <c r="G63">
-        <v>2619573.323269641</v>
+        <v>3008339.0858126287</v>
+      </c>
+      <c r="H63">
+        <v>2803294.517230832</v>
       </c>
     </row>
     <row r="64">
@@ -1173,22 +1237,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
+        <v>260064050</v>
+      </c>
+      <c r="C66">
         <v>289953113</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>405789909</v>
       </c>
-      <c r="D66">
-        <v>314373774.2107317</v>
-      </c>
       <c r="E66">
-        <v>222275087.84406367</v>
+        <v>336422069.112434</v>
       </c>
       <c r="F66">
-        <v>150894696.82623056</v>
+        <v>237864132.1223011</v>
       </c>
       <c r="G66">
-        <v>90285965.17272408</v>
+        <v>161477547.7115514</v>
+      </c>
+      <c r="H66">
+        <v>96618082.38132645</v>
       </c>
     </row>
     <row r="67">
@@ -1201,22 +1268,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
+        <v>103870666</v>
+      </c>
+      <c r="C68">
         <v>118922802</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>133161208</v>
       </c>
-      <c r="D68">
-        <v>162877657.73468915</v>
-      </c>
       <c r="E68">
-        <v>110409931.11272188</v>
+        <v>174300921.77651003</v>
       </c>
       <c r="F68">
-        <v>131408180.43006398</v>
+        <v>118153422.84437673</v>
       </c>
       <c r="G68">
-        <v>107949886.94861042</v>
+        <v>140624363.6880097</v>
+      </c>
+      <c r="H68">
+        <v>115520845.90669753</v>
       </c>
     </row>
     <row r="69">
@@ -1244,22 +1314,25 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B73">
+        <v>9792819</v>
+      </c>
+      <c r="C73">
         <v>9238284</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>44354466</v>
       </c>
-      <c r="D73">
-        <v>66372708.88698095</v>
-      </c>
       <c r="E73">
-        <v>174840727.77633777</v>
+        <v>71027693.4277208</v>
       </c>
       <c r="F73">
-        <v>160111308.3251822</v>
+        <v>187103009.94831342</v>
       </c>
       <c r="G73">
-        <v>46028044.74048621</v>
+        <v>171340557.17685214</v>
+      </c>
+      <c r="H73">
+        <v>49256176.3069149</v>
       </c>
     </row>
     <row r="74">
@@ -1297,22 +1370,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
+        <v>3823524</v>
+      </c>
+      <c r="C80">
         <v>1856676</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>3066240</v>
       </c>
-      <c r="D80">
-        <v>2603943.1600667615</v>
-      </c>
       <c r="E80">
-        <v>1959032.9424366867</v>
+        <v>2786568.1479321225</v>
       </c>
       <c r="F80">
-        <v>605012.8303763936</v>
+        <v>2096427.7876187796</v>
       </c>
       <c r="G80">
-        <v>278857.91280641005</v>
+        <v>647444.8091155316</v>
+      </c>
+      <c r="H80">
+        <v>298415.3377623084</v>
       </c>
     </row>
     <row r="81">
@@ -1325,35 +1401,35 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
+        <v>211235154</v>
+      </c>
+      <c r="C82">
         <v>197643862</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>168065479</v>
       </c>
-      <c r="D82">
-        <v>176198071.87645</v>
-      </c>
       <c r="E82">
-        <v>155325825.68040365</v>
+        <v>188555550.0394955</v>
       </c>
       <c r="F82">
-        <v>148872771.97828475</v>
+        <v>166219449.42191944</v>
       </c>
       <c r="G82">
-        <v>68865963.94176799</v>
+        <v>159313817.15659803</v>
+      </c>
+      <c r="H82">
+        <v>73695810.46917042</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
       </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
       <c r="C83">
         <v>0</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>0</v>
       </c>
     </row>
@@ -1362,22 +1438,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
+        <v>328722163</v>
+      </c>
+      <c r="C84">
         <v>327661624</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>348647393</v>
       </c>
-      <c r="D84">
-        <v>408052381.65818685</v>
-      </c>
       <c r="E84">
-        <v>442535517.5119</v>
+        <v>436670733.3916584</v>
       </c>
       <c r="F84">
-        <v>440997273.5639073</v>
+        <v>473572310.0022284</v>
       </c>
       <c r="G84">
-        <v>223122753.54367104</v>
+        <v>471926182.83057547</v>
+      </c>
+      <c r="H84">
+        <v>238771248.02054518</v>
       </c>
     </row>
     <row r="85">
@@ -1390,22 +1469,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
+        <v>2119263807</v>
+      </c>
+      <c r="C86">
         <v>2062053729</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>1337316020</v>
       </c>
-      <c r="D86">
-        <v>1467643315.1858566</v>
-      </c>
       <c r="E86">
-        <v>1328853552.9943054</v>
+        <v>1570575033.0270493</v>
       </c>
       <c r="F86">
-        <v>1134726857.4558418</v>
+        <v>1422051387.613785</v>
       </c>
       <c r="G86">
-        <v>510577276.7819269</v>
+        <v>1214309807.5568185</v>
+      </c>
+      <c r="H86">
+        <v>546386111.0170943</v>
       </c>
     </row>
     <row r="87">
@@ -1416,7 +1498,7 @@
         <v>182837401</v>
       </c>
       <c r="C87">
-        <v>147337401</v>
+        <v>182837401</v>
       </c>
       <c r="D87">
         <v>147337401</v>
@@ -1428,6 +1510,9 @@
         <v>147337401</v>
       </c>
       <c r="G87">
+        <v>147337401</v>
+      </c>
+      <c r="H87">
         <v>105241000</v>
       </c>
     </row>
@@ -1435,17 +1520,17 @@
       <c r="A88" t="str">
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
-      <c r="D88">
-        <v>21857193.336794145</v>
-      </c>
       <c r="E88">
-        <v>14795922.641096568</v>
+        <v>33723489.50312426</v>
       </c>
       <c r="F88">
-        <v>21857193.336794145</v>
+        <v>26166983.544655915</v>
       </c>
       <c r="G88">
-        <v>15612280.848890178</v>
+        <v>33723489.50312426</v>
+      </c>
+      <c r="H88">
+        <v>24088206.624455795</v>
       </c>
     </row>
     <row r="89">
@@ -1478,22 +1563,25 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>32259000</v>
+        <v>662378714</v>
       </c>
       <c r="C94">
         <v>32259000</v>
       </c>
       <c r="D94">
-        <v>37044554.754367106</v>
+        <v>32259000</v>
       </c>
       <c r="E94">
-        <v>35498514.64624474</v>
+        <v>39642638.10205452</v>
       </c>
       <c r="F94">
-        <v>37044554.754367106</v>
+        <v>37988167.99426275</v>
       </c>
       <c r="G94">
-        <v>82978470.56622377</v>
+        <v>39642638.10205452</v>
+      </c>
+      <c r="H94">
+        <v>88798083.84067571</v>
       </c>
     </row>
     <row r="95">
@@ -1511,22 +1599,25 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
+        <v>1037154916</v>
+      </c>
+      <c r="C97">
         <v>918114546</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>867305744</v>
       </c>
-      <c r="D97">
-        <v>942513588.2173069</v>
-      </c>
       <c r="E97">
-        <v>677981694.3269558</v>
+        <v>1008615850.0680265</v>
       </c>
       <c r="F97">
-        <v>484405743.832776</v>
+        <v>725531272.4430245</v>
       </c>
       <c r="G97">
-        <v>185764473.58935264</v>
+        <v>518379063.3913734</v>
+      </c>
+      <c r="H97">
+        <v>198792881.9107543</v>
       </c>
     </row>
     <row r="98">
@@ -1539,8 +1630,11 @@
       <c r="C98">
         <v>197610988</v>
       </c>
-      <c r="E98">
-        <v>217455486.8959637</v>
+      <c r="D98">
+        <v>197610988</v>
+      </c>
+      <c r="F98">
+        <v>232706513.21046028</v>
       </c>
     </row>
     <row r="99">
@@ -1552,20 +1646,23 @@
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
-        <v>226926162.15724546</v>
-      </c>
-      <c r="F100">
-        <v>207178790.49822703</v>
+      <c r="E100">
+        <v>242841404.94973305</v>
       </c>
       <c r="G100">
-        <v>283454.7494312816</v>
+        <v>221709070.83650017</v>
+      </c>
+      <c r="H100">
+        <v>303334.5689946009</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
         <v xml:space="preserve">    Diğer Yedekler</v>
       </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -1580,19 +1677,22 @@
         <v>92802887</v>
       </c>
       <c r="C103">
+        <v>92802887</v>
+      </c>
+      <c r="D103">
         <v>214267367</v>
       </c>
-      <c r="D103">
-        <v>246053479.92515486</v>
-      </c>
       <c r="E103">
-        <v>227016112.05584726</v>
+        <v>263310198.30314326</v>
       </c>
       <c r="F103">
-        <v>120697597.02802905</v>
+        <v>242937663.39584565</v>
       </c>
       <c r="G103">
-        <v>114948079.79125214</v>
+        <v>129162604.07221389</v>
+      </c>
+      <c r="H103">
+        <v>123009850.10903655</v>
       </c>
     </row>
     <row r="104">
@@ -1600,22 +1700,25 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
+        <v>-53521099</v>
+      </c>
+      <c r="C104">
         <v>8309193</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>-121464480</v>
       </c>
-      <c r="D104">
-        <v>-154089064.20501184</v>
-      </c>
       <c r="E104">
-        <v>8768421.4281974</v>
+        <v>-164895948.89903244</v>
       </c>
       <c r="F104">
-        <v>116205577.00564857</v>
+        <v>9383386.025535949</v>
       </c>
       <c r="G104">
-        <v>5749517.236776926</v>
+        <v>124355540.65155233</v>
+      </c>
+      <c r="H104">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="105">
@@ -1628,22 +1731,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
+        <v>2119263807</v>
+      </c>
+      <c r="C106">
         <v>2062053729</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>1337316020</v>
       </c>
-      <c r="D106">
-        <v>1467643315.1858566</v>
-      </c>
       <c r="E106">
-        <v>1328853552.9943054</v>
+        <v>1570575033.0270493</v>
       </c>
       <c r="F106">
-        <v>1134726857.4558418</v>
+        <v>1422051387.613785</v>
       </c>
       <c r="G106">
-        <v>510577276.7819269</v>
+        <v>1214309807.5568185</v>
+      </c>
+      <c r="H106">
+        <v>546386111.0170943</v>
       </c>
     </row>
     <row r="107">
@@ -1651,39 +1757,45 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
+        <v>2708050020</v>
+      </c>
+      <c r="C107">
         <v>2679668466</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>2091753322</v>
       </c>
-      <c r="D107">
-        <v>2190069471.054775</v>
-      </c>
       <c r="E107">
-        <v>1993664158.350269</v>
+        <v>2343667835.5311418</v>
       </c>
       <c r="F107">
-        <v>1726618827.8459797</v>
+        <v>2133487829.7383144</v>
       </c>
       <c r="G107">
-        <v>823985995.498322</v>
+        <v>1847713538.0989454</v>
+      </c>
+      <c r="H107">
+        <v>881775441.4189658</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="C108">
+        <v>320750414</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1694,6 +1806,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1701,27 +1815,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1735,28 +1855,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>304265642</v>
+      </c>
+      <c r="C3">
         <v>211080076</v>
       </c>
-      <c r="C3">
-        <v>278053116.3356527</v>
-      </c>
       <c r="D3">
-        <v>175081369.00410426</v>
+        <v>297554097.6840407</v>
       </c>
       <c r="E3">
+        <v>187360528.31148544</v>
+      </c>
+      <c r="F3">
+        <v>116106949</v>
+      </c>
+      <c r="G3">
         <v>14706224</v>
       </c>
-      <c r="F3">
-        <v>158071626.26964003</v>
-      </c>
-      <c r="G3">
-        <v>80660549.86148217</v>
-      </c>
       <c r="H3">
-        <v>313299477.5294634</v>
+        <v>169157824.0300438</v>
       </c>
       <c r="I3">
-        <v>105062625.69251193</v>
+        <v>86317598.05115497</v>
+      </c>
+      <c r="J3">
+        <v>335272427.6919298</v>
+      </c>
+      <c r="K3">
+        <v>112431089.42722188</v>
       </c>
     </row>
     <row r="4">
@@ -1779,28 +1905,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-268263695</v>
+      </c>
+      <c r="C7">
         <v>-165471191</v>
       </c>
-      <c r="C7">
-        <v>-201355187.7931853</v>
-      </c>
       <c r="D7">
-        <v>-177246539.91685724</v>
+        <v>-215477035.4937377</v>
       </c>
       <c r="E7">
+        <v>-189677551.35286087</v>
+      </c>
+      <c r="F7">
+        <v>-111792549</v>
+      </c>
+      <c r="G7">
         <v>-21439170</v>
       </c>
-      <c r="F7">
-        <v>-105386171.06405188</v>
-      </c>
-      <c r="G7">
-        <v>-89357796.90948023</v>
-      </c>
       <c r="H7">
-        <v>-158785184.69221494</v>
+        <v>-112777326.33460544</v>
       </c>
       <c r="I7">
-        <v>-82838737.2976283</v>
+        <v>-95624817.95146443</v>
+      </c>
+      <c r="J7">
+        <v>-169921427.1695167</v>
+      </c>
+      <c r="K7">
+        <v>-88648550.51696652</v>
       </c>
     </row>
     <row r="8">
@@ -1808,28 +1940,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>36001947</v>
+      </c>
+      <c r="C8">
         <v>45608885</v>
       </c>
-      <c r="C8">
-        <v>76697928.54246742</v>
-      </c>
       <c r="D8">
-        <v>-2165170.9127529534</v>
+        <v>82077062.190303</v>
       </c>
       <c r="E8">
+        <v>-2317023.041375378</v>
+      </c>
+      <c r="F8">
+        <v>4314400</v>
+      </c>
+      <c r="G8">
         <v>-6732946</v>
       </c>
-      <c r="F8">
-        <v>52685455.20558814</v>
-      </c>
-      <c r="G8">
-        <v>-8697247.047998052</v>
-      </c>
       <c r="H8">
-        <v>154514292.83724853</v>
+        <v>56380497.69543837</v>
       </c>
       <c r="I8">
-        <v>22223888.39488361</v>
+        <v>-9307219.900309457</v>
+      </c>
+      <c r="J8">
+        <v>165351000.52241316</v>
+      </c>
+      <c r="K8">
+        <v>23782538.910255343</v>
       </c>
     </row>
     <row r="9">
@@ -1857,28 +1995,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>36001947</v>
+      </c>
+      <c r="C13">
         <v>45608885</v>
       </c>
-      <c r="C13">
-        <v>76697928.54246742</v>
-      </c>
       <c r="D13">
-        <v>-2165170.9127529534</v>
+        <v>82077062.190303</v>
       </c>
       <c r="E13">
+        <v>-2317023.041375378</v>
+      </c>
+      <c r="F13">
+        <v>4314400</v>
+      </c>
+      <c r="G13">
         <v>-6732946</v>
       </c>
-      <c r="F13">
-        <v>52685455.20558814</v>
-      </c>
-      <c r="G13">
-        <v>-8697247.047998052</v>
-      </c>
       <c r="H13">
-        <v>154514292.83724853</v>
+        <v>56380497.69543837</v>
       </c>
       <c r="I13">
-        <v>22223888.39488361</v>
+        <v>-9307219.900309457</v>
+      </c>
+      <c r="J13">
+        <v>165351000.52241316</v>
+      </c>
+      <c r="K13">
+        <v>23782538.910255343</v>
       </c>
     </row>
     <row r="14"/>
@@ -1887,28 +2031,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-30536186</v>
+      </c>
+      <c r="C15">
         <v>-19628916</v>
       </c>
-      <c r="C15">
-        <v>-26126545.84120642</v>
-      </c>
       <c r="D15">
-        <v>-21290361.9403603</v>
+        <v>-27958905.391286537</v>
       </c>
       <c r="E15">
+        <v>-22783540.49764792</v>
+      </c>
+      <c r="F15">
+        <v>-13297880</v>
+      </c>
+      <c r="G15">
         <v>-7242752</v>
       </c>
-      <c r="F15">
-        <v>-25333128.344008174</v>
-      </c>
-      <c r="G15">
-        <v>-20437116.487197153</v>
-      </c>
       <c r="H15">
-        <v>-12226911.341943799</v>
+        <v>-27109842.33967677</v>
       </c>
       <c r="I15">
-        <v>-5303564.37007383</v>
+        <v>-21870453.515330154</v>
+      </c>
+      <c r="J15">
+        <v>-13084433.721731875</v>
+      </c>
+      <c r="K15">
+        <v>-5675524.631565507</v>
       </c>
     </row>
     <row r="16">
@@ -1916,28 +2066,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-37034153</v>
+      </c>
+      <c r="C16">
         <v>-18346071</v>
       </c>
-      <c r="C16">
-        <v>-36402457.43289877</v>
-      </c>
       <c r="D16">
-        <v>-30191521.124126133</v>
+        <v>-38955507.91760367</v>
       </c>
       <c r="E16">
+        <v>-32308973.71045254</v>
+      </c>
+      <c r="F16">
+        <v>-16205969</v>
+      </c>
+      <c r="G16">
         <v>-10315040</v>
       </c>
-      <c r="F16">
-        <v>-30341752.087493278</v>
-      </c>
-      <c r="G16">
-        <v>-23948308.456899162</v>
-      </c>
       <c r="H16">
-        <v>-25112231.394699488</v>
+        <v>-32469740.974412832</v>
       </c>
       <c r="I16">
-        <v>-214011.85550691668</v>
+        <v>-25627899.47424879</v>
+      </c>
+      <c r="J16">
+        <v>-26873453.000478145</v>
+      </c>
+      <c r="K16">
+        <v>-229021.36612695342</v>
       </c>
     </row>
     <row r="17">
@@ -1950,25 +2106,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>667199</v>
+      </c>
+      <c r="C18">
         <v>0</v>
       </c>
-      <c r="C18">
-        <v>4193117.474641919</v>
-      </c>
       <c r="D18">
-        <v>403917.591995771</v>
+        <v>4487197.637246114</v>
       </c>
       <c r="E18">
+        <v>432245.95433027844</v>
+      </c>
+      <c r="F18">
+        <v>351764</v>
+      </c>
+      <c r="G18">
         <v>25031</v>
       </c>
-      <c r="F18">
-        <v>24479460.5391776</v>
-      </c>
-      <c r="G18">
-        <v>18732438.82219754</v>
+      <c r="H18">
+        <v>26196303.384473532</v>
       </c>
       <c r="I18">
-        <v>259280.8778873967</v>
+        <v>20046219.961915176</v>
+      </c>
+      <c r="K18">
+        <v>277465.286788508</v>
       </c>
     </row>
     <row r="19">
@@ -1976,28 +2138,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-245162</v>
+      </c>
+      <c r="C19">
         <v>-65807</v>
       </c>
-      <c r="C19">
-        <v>-798453.0284614968</v>
-      </c>
       <c r="D19">
-        <v>-2431516.426892214</v>
+        <v>-854451.7448966524</v>
       </c>
       <c r="E19">
+        <v>-2602048.4357184866</v>
+      </c>
+      <c r="F19">
+        <v>-6814886</v>
+      </c>
+      <c r="G19">
         <v>-293209</v>
       </c>
-      <c r="F19">
-        <v>-19797634.631554384</v>
-      </c>
-      <c r="G19">
-        <v>-11909106.061920516</v>
-      </c>
       <c r="H19">
-        <v>-20160407.13330284</v>
+        <v>-21186122.22982353</v>
       </c>
       <c r="I19">
-        <v>-714951.0644804913</v>
+        <v>-12744339.48152779</v>
+      </c>
+      <c r="J19">
+        <v>-21574337.42354227</v>
+      </c>
+      <c r="K19">
+        <v>-765093.4529463475</v>
       </c>
     </row>
     <row r="20">
@@ -2010,28 +2178,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-31146355</v>
+      </c>
+      <c r="C21">
         <v>7568091</v>
       </c>
-      <c r="C21">
-        <v>17563589.714542653</v>
-      </c>
       <c r="D21">
-        <v>-55674652.81213582</v>
+        <v>18795394.773762263</v>
       </c>
       <c r="E21">
+        <v>-59579339.73086404</v>
+      </c>
+      <c r="F21">
+        <v>-31652571</v>
+      </c>
+      <c r="G21">
         <v>-24558916</v>
       </c>
-      <c r="F21">
-        <v>1692400.6817099096</v>
-      </c>
-      <c r="G21">
-        <v>-46259339.23181734</v>
-      </c>
       <c r="H21">
-        <v>97014742.9673024</v>
+        <v>1811095.5359987707</v>
       </c>
       <c r="I21">
-        <v>16250641.982709773</v>
+        <v>-49503692.409501016</v>
+      </c>
+      <c r="J21">
+        <v>103818776.37666087</v>
+      </c>
+      <c r="K21">
+        <v>17390364.74640505</v>
       </c>
     </row>
     <row r="22"/>
@@ -2050,38 +2224,38 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>9817281</v>
+      </c>
+      <c r="C25">
         <v>2249161</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0</v>
       </c>
-      <c r="F25">
-        <v>24894100.664947763</v>
+      <c r="G25">
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>26621147.897292126</v>
-      </c>
-      <c r="I25">
-        <v>814089.0866293263</v>
+        <v>26640023.886919554</v>
+      </c>
+      <c r="J25">
+        <v>28488195.875244267</v>
+      </c>
+      <c r="K25">
+        <v>871184.4225978702</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>-1762994.9565351023</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
+      <c r="D26">
+        <v>-1886640.8707322697</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
@@ -2120,28 +2294,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-21329074</v>
+      </c>
+      <c r="C33">
         <v>9817252</v>
       </c>
-      <c r="C33">
-        <v>15800594.758007552</v>
-      </c>
       <c r="D33">
-        <v>-55674652.81213582</v>
+        <v>16908753.903029993</v>
       </c>
       <c r="E33">
+        <v>-59579339.73086404</v>
+      </c>
+      <c r="F33">
+        <v>-31652571</v>
+      </c>
+      <c r="G33">
         <v>-24558916</v>
       </c>
-      <c r="F33">
-        <v>26586501.346657675</v>
-      </c>
-      <c r="G33">
-        <v>-46259339.23181734</v>
-      </c>
       <c r="H33">
-        <v>123635890.86459453</v>
+        <v>28451119.422918327</v>
       </c>
       <c r="I33">
-        <v>17064731.0693391</v>
+        <v>-49503692.409501016</v>
+      </c>
+      <c r="J33">
+        <v>132306972.25190516</v>
+      </c>
+      <c r="K33">
+        <v>18261549.16900292</v>
       </c>
     </row>
     <row r="34"/>
@@ -2150,28 +2330,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>173691754</v>
+      </c>
+      <c r="C35">
         <v>93081404</v>
       </c>
-      <c r="C35">
-        <v>19475225.278795175</v>
-      </c>
       <c r="D35">
-        <v>15301302.777668225</v>
+        <v>20841101.01477858</v>
       </c>
       <c r="E35">
+        <v>16374444.571602095</v>
+      </c>
+      <c r="F35">
+        <v>8543803</v>
+      </c>
+      <c r="G35">
         <v>6798996</v>
       </c>
-      <c r="F35">
-        <v>37762537.26051903</v>
-      </c>
-      <c r="G35">
-        <v>45379204.06433794</v>
-      </c>
       <c r="H35">
-        <v>33284241.340607386</v>
+        <v>40410975.60384704</v>
       </c>
       <c r="I35">
-        <v>8244887.548387096</v>
+        <v>48561829.82924787</v>
+      </c>
+      <c r="J35">
+        <v>35618598.81205862</v>
+      </c>
+      <c r="K35">
+        <v>8823134.612903226</v>
       </c>
     </row>
     <row r="36">
@@ -2179,28 +2365,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-178397590</v>
+      </c>
+      <c r="C36">
         <v>-71528823</v>
       </c>
-      <c r="C36">
-        <v>-172630218.68595594</v>
-      </c>
       <c r="D36">
-        <v>-127383516.18245913</v>
+        <v>-184737468.9808929</v>
       </c>
       <c r="E36">
+        <v>-136317433.57890192</v>
+      </c>
+      <c r="F36">
+        <v>-82038696</v>
+      </c>
+      <c r="G36">
         <v>-57054251</v>
       </c>
-      <c r="F36">
-        <v>-75585463.48184764</v>
-      </c>
-      <c r="G36">
-        <v>-42680934.45980363</v>
-      </c>
       <c r="H36">
-        <v>-27964172.914582357</v>
+        <v>-80886575.4887688</v>
       </c>
       <c r="I36">
-        <v>-12653739.62279863</v>
+        <v>-45674319.74460535</v>
+      </c>
+      <c r="J36">
+        <v>-29925412.628839225</v>
+      </c>
+      <c r="K36">
+        <v>-13541197.183510434</v>
       </c>
     </row>
     <row r="37">
@@ -2213,28 +2405,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>-26034910</v>
+      </c>
+      <c r="C38">
         <v>31369833</v>
       </c>
-      <c r="C38">
-        <v>-137354398.6491532</v>
-      </c>
       <c r="D38">
-        <v>-167756866.21692672</v>
+        <v>-146987614.0630843</v>
       </c>
       <c r="E38">
+        <v>-179522328.73816386</v>
+      </c>
+      <c r="F38">
+        <v>-105147464</v>
+      </c>
+      <c r="G38">
         <v>-74814171</v>
       </c>
-      <c r="F38">
-        <v>-11236424.874670947</v>
-      </c>
-      <c r="G38">
-        <v>-43561069.62728304</v>
-      </c>
       <c r="H38">
-        <v>128955959.29061957</v>
+        <v>-12024480.462003434</v>
       </c>
       <c r="I38">
-        <v>12655878.994927566</v>
+        <v>-46616182.324858494</v>
+      </c>
+      <c r="J38">
+        <v>138000158.43512455</v>
+      </c>
+      <c r="K38">
+        <v>13543486.59839571</v>
       </c>
     </row>
     <row r="39"/>
@@ -2243,45 +2441,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>-27486189</v>
+      </c>
+      <c r="C40">
         <v>-23060640</v>
       </c>
-      <c r="C40">
-        <v>3692207.562061203</v>
-      </c>
       <c r="D40">
-        <v>13667802.011914873</v>
+        <v>3951156.901493226</v>
       </c>
       <c r="E40">
+        <v>14626379.839131393</v>
+      </c>
+      <c r="F40">
+        <v>704202</v>
+      </c>
+      <c r="G40">
         <v>7778203</v>
       </c>
-      <c r="F40">
-        <v>20004846.302868348</v>
-      </c>
-      <c r="G40">
-        <v>34387670.45963139</v>
-      </c>
       <c r="H40">
-        <v>-12750382.284970986</v>
+        <v>21407866.487539385</v>
       </c>
       <c r="I40">
-        <v>-6906361.758150641</v>
+        <v>36799415.84513635</v>
+      </c>
+      <c r="J40">
+        <v>-13644617.783572208</v>
+      </c>
+      <c r="K40">
+        <v>-7390732.635218372</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>-35695070.28016583</v>
-      </c>
-      <c r="I41">
-        <v>-2968228.9695000625</v>
+      <c r="J41">
+        <v>-38198508.86390257</v>
+      </c>
+      <c r="K41">
+        <v>-3176402.783679119</v>
       </c>
     </row>
     <row r="42">
@@ -2289,28 +2487,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>-27486189</v>
+      </c>
+      <c r="C42">
         <v>-23060640</v>
       </c>
-      <c r="C42">
-        <v>3692207.562061203</v>
-      </c>
       <c r="D42">
-        <v>13667802.011914873</v>
+        <v>3951156.901493226</v>
       </c>
       <c r="E42">
+        <v>14626379.839131393</v>
+      </c>
+      <c r="F42">
+        <v>704202</v>
+      </c>
+      <c r="G42">
         <v>7778203</v>
       </c>
-      <c r="F42">
-        <v>20004846.302868348</v>
-      </c>
-      <c r="G42">
-        <v>34387670.45963139</v>
-      </c>
       <c r="H42">
-        <v>22944687.99519485</v>
+        <v>21407866.487539385</v>
       </c>
       <c r="I42">
-        <v>-3938132.788650578</v>
+        <v>36799415.84513635</v>
+      </c>
+      <c r="J42">
+        <v>24553891.080330364</v>
+      </c>
+      <c r="K42">
+        <v>-4214329.851539252</v>
       </c>
     </row>
     <row r="43">
@@ -2318,28 +2522,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>-53521099</v>
+      </c>
+      <c r="C43">
         <v>8309193</v>
       </c>
-      <c r="C43">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D43">
-        <v>-154089064.20501184</v>
+        <v>-143036457.16159108</v>
       </c>
       <c r="E43">
+        <v>-164895948.89903244</v>
+      </c>
+      <c r="F43">
+        <v>-104443262</v>
+      </c>
+      <c r="G43">
         <v>-67035968</v>
       </c>
-      <c r="F43">
-        <v>8768421.4281974</v>
-      </c>
-      <c r="G43">
-        <v>-9173399.167651653</v>
-      </c>
       <c r="H43">
-        <v>116205577.00564857</v>
+        <v>9383386.025535949</v>
       </c>
       <c r="I43">
-        <v>5749517.236776926</v>
+        <v>-9816766.479722146</v>
+      </c>
+      <c r="J43">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K43">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="44">
@@ -2353,28 +2563,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>-53521099</v>
+      </c>
+      <c r="C46">
         <v>8309193</v>
       </c>
-      <c r="C46">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D46">
-        <v>-154089064.20501184</v>
+        <v>-143036457.16159108</v>
       </c>
       <c r="E46">
+        <v>-164895948.89903244</v>
+      </c>
+      <c r="F46">
+        <v>-104443262</v>
+      </c>
+      <c r="G46">
         <v>-67035968</v>
       </c>
-      <c r="F46">
-        <v>8768421.4281974</v>
-      </c>
-      <c r="G46">
-        <v>-9173399.167651653</v>
-      </c>
       <c r="H46">
-        <v>116205577.00564857</v>
+        <v>9383386.025535949</v>
       </c>
       <c r="I46">
-        <v>5749517.236776926</v>
+        <v>-9816766.479722146</v>
+      </c>
+      <c r="J46">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K46">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="47">
@@ -2387,10 +2603,16 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="D47">
         <v>0</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -2399,28 +2621,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>-53521099</v>
+      </c>
+      <c r="C48">
         <v>8309193</v>
       </c>
-      <c r="C48">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D48">
-        <v>-154089064.20501184</v>
+        <v>-143036457.16159108</v>
       </c>
       <c r="E48">
+        <v>-164895948.89903244</v>
+      </c>
+      <c r="F48">
+        <v>-104443262</v>
+      </c>
+      <c r="G48">
         <v>-67035968</v>
       </c>
-      <c r="F48">
-        <v>8768421.4281974</v>
-      </c>
-      <c r="G48">
-        <v>-9173399.167651653</v>
-      </c>
       <c r="H48">
-        <v>116205577.00564857</v>
+        <v>9383386.025535949</v>
       </c>
       <c r="I48">
-        <v>5749517.236776926</v>
+        <v>-9816766.479722146</v>
+      </c>
+      <c r="J48">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K48">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="49"/>
@@ -2429,40 +2657,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>22132445</v>
+      </c>
+      <c r="C50">
         <v>10734557</v>
       </c>
-      <c r="C50">
-        <v>42939214.156960845</v>
-      </c>
       <c r="D50">
-        <v>32016252.81983951</v>
+        <v>45950713.63383962</v>
       </c>
       <c r="E50">
+        <v>34261681.16573613</v>
+      </c>
+      <c r="F50">
+        <v>17942673</v>
+      </c>
+      <c r="G50">
         <v>8618763</v>
       </c>
-      <c r="F50">
-        <v>41219091.64317405</v>
-      </c>
-      <c r="G50">
-        <v>33610739.61419806</v>
-      </c>
       <c r="H50">
-        <v>20612617.34768741</v>
+        <v>44109952.02238558</v>
       </c>
       <c r="I50">
-        <v>12490219.4759</v>
+        <v>35967995.720368735</v>
+      </c>
+      <c r="J50">
+        <v>22058262.955749847</v>
+      </c>
+      <c r="K50">
+        <v>13366208.712225517</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2473,6 +2707,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2480,27 +2716,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2514,16 +2756,22 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>93185566</v>
+      </c>
+      <c r="C3">
         <v>211080076</v>
       </c>
-      <c r="C3">
-        <v>102971747.33154845</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>110193569.37255529</v>
+      </c>
+      <c r="F3">
+        <v>101400725</v>
+      </c>
+      <c r="G3">
         <v>14706224</v>
       </c>
-      <c r="F3">
-        <v>77411076.40815786</v>
+      <c r="H3">
+        <v>82840225.97888884</v>
       </c>
     </row>
     <row r="4">
@@ -2546,16 +2794,22 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-102792504</v>
+      </c>
+      <c r="C7">
         <v>-165471191</v>
       </c>
-      <c r="C7">
-        <v>-24108647.87632805</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>-25799484.14087683</v>
+      </c>
+      <c r="F7">
+        <v>-90353379</v>
+      </c>
+      <c r="G7">
         <v>-21439170</v>
       </c>
-      <c r="F7">
-        <v>-16028374.154571652</v>
+      <c r="H7">
+        <v>-17152508.38314101</v>
       </c>
     </row>
     <row r="8">
@@ -2563,16 +2817,22 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>-9606938</v>
+      </c>
+      <c r="C8">
         <v>45608885</v>
       </c>
-      <c r="C8">
-        <v>78863099.45522037</v>
-      </c>
-      <c r="E8">
+      <c r="D8">
+        <v>84394085.23167838</v>
+      </c>
+      <c r="F8">
+        <v>11047346</v>
+      </c>
+      <c r="G8">
         <v>-6732946</v>
       </c>
-      <c r="F8">
-        <v>61382702.25358619</v>
+      <c r="H8">
+        <v>65687717.59574783</v>
       </c>
     </row>
     <row r="9">
@@ -2600,16 +2860,22 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>-9606938</v>
+      </c>
+      <c r="C13">
         <v>45608885</v>
       </c>
-      <c r="C13">
-        <v>78863099.45522037</v>
-      </c>
-      <c r="E13">
+      <c r="D13">
+        <v>84394085.23167838</v>
+      </c>
+      <c r="F13">
+        <v>11047346</v>
+      </c>
+      <c r="G13">
         <v>-6732946</v>
       </c>
-      <c r="F13">
-        <v>61382702.25358619</v>
+      <c r="H13">
+        <v>65687717.59574783</v>
       </c>
     </row>
     <row r="14"/>
@@ -2618,16 +2884,22 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-10907270</v>
+      </c>
+      <c r="C15">
         <v>-19628916</v>
       </c>
-      <c r="C15">
-        <v>-4836183.90084612</v>
-      </c>
-      <c r="E15">
+      <c r="D15">
+        <v>-5175364.893638618</v>
+      </c>
+      <c r="F15">
+        <v>-6055128</v>
+      </c>
+      <c r="G15">
         <v>-7242752</v>
       </c>
-      <c r="F15">
-        <v>-4896011.8568110205</v>
+      <c r="H15">
+        <v>-5239388.824346617</v>
       </c>
     </row>
     <row r="16">
@@ -2635,16 +2907,22 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-18688082</v>
+      </c>
+      <c r="C16">
         <v>-18346071</v>
       </c>
-      <c r="C16">
-        <v>-6210936.308772635</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
+        <v>-6646534.20715113</v>
+      </c>
+      <c r="F16">
+        <v>-5890929</v>
+      </c>
+      <c r="G16">
         <v>-10315040</v>
       </c>
-      <c r="F16">
-        <v>-6393443.630594116</v>
+      <c r="H16">
+        <v>-6841841.500164043</v>
       </c>
     </row>
     <row r="17">
@@ -2657,16 +2935,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>667199</v>
+      </c>
+      <c r="C18">
         <v>0</v>
       </c>
-      <c r="C18">
-        <v>3789199.882646148</v>
-      </c>
-      <c r="E18">
+      <c r="D18">
+        <v>4054951.6829158356</v>
+      </c>
+      <c r="F18">
+        <v>326733</v>
+      </c>
+      <c r="G18">
         <v>25031</v>
       </c>
-      <c r="F18">
-        <v>5747021.716980059</v>
+      <c r="H18">
+        <v>6150083.422558356</v>
       </c>
     </row>
     <row r="19">
@@ -2674,16 +2958,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-179355</v>
+      </c>
+      <c r="C19">
         <v>-65807</v>
       </c>
-      <c r="C19">
-        <v>1633063.3984307172</v>
-      </c>
-      <c r="E19">
+      <c r="D19">
+        <v>1747596.6908218341</v>
+      </c>
+      <c r="F19">
+        <v>-6521677</v>
+      </c>
+      <c r="G19">
         <v>-293209</v>
       </c>
-      <c r="F19">
-        <v>-7888528.569633868</v>
+      <c r="H19">
+        <v>-8441782.74829574</v>
       </c>
     </row>
     <row r="20">
@@ -2696,16 +2986,22 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-38714446</v>
+      </c>
+      <c r="C21">
         <v>7568091</v>
       </c>
-      <c r="C21">
-        <v>73238242.52667847</v>
-      </c>
-      <c r="E21">
+      <c r="D21">
+        <v>78374734.5046263</v>
+      </c>
+      <c r="F21">
+        <v>-7093655</v>
+      </c>
+      <c r="G21">
         <v>-24558916</v>
       </c>
-      <c r="F21">
-        <v>47951739.91352725</v>
+      <c r="H21">
+        <v>51314787.945499785</v>
       </c>
     </row>
     <row r="22"/>
@@ -2724,9 +3020,15 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>7568120</v>
+      </c>
+      <c r="C25">
         <v>2249161</v>
       </c>
-      <c r="E25">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
@@ -2734,12 +3036,6 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2776,16 +3072,22 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-31146326</v>
+      </c>
+      <c r="C33">
         <v>9817252</v>
       </c>
-      <c r="C33">
-        <v>71475247.57014337</v>
-      </c>
-      <c r="E33">
+      <c r="D33">
+        <v>76488093.63389403</v>
+      </c>
+      <c r="F33">
+        <v>-7093655</v>
+      </c>
+      <c r="G33">
         <v>-24558916</v>
       </c>
-      <c r="F33">
-        <v>72845840.57847501</v>
+      <c r="H33">
+        <v>77954811.83241934</v>
       </c>
     </row>
     <row r="34"/>
@@ -2794,16 +3096,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>80610350</v>
+      </c>
+      <c r="C35">
         <v>93081404</v>
       </c>
-      <c r="C35">
-        <v>4173922.5011269506</v>
-      </c>
-      <c r="E35">
+      <c r="D35">
+        <v>4466656.443176486</v>
+      </c>
+      <c r="F35">
+        <v>1744807</v>
+      </c>
+      <c r="G35">
         <v>6798996</v>
       </c>
-      <c r="F35">
-        <v>-7616666.803818911</v>
+      <c r="H35">
+        <v>-8150854.225400828</v>
       </c>
     </row>
     <row r="36">
@@ -2811,16 +3119,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-106868767</v>
+      </c>
+      <c r="C36">
         <v>-71528823</v>
       </c>
-      <c r="C36">
-        <v>-45246702.50349681</v>
-      </c>
-      <c r="E36">
+      <c r="D36">
+        <v>-48420035.40199098</v>
+      </c>
+      <c r="F36">
+        <v>-24984445</v>
+      </c>
+      <c r="G36">
         <v>-57054251</v>
       </c>
-      <c r="F36">
-        <v>-32904529.02204401</v>
+      <c r="H36">
+        <v>-35212255.74416345</v>
       </c>
     </row>
     <row r="37">
@@ -2833,16 +3147,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>-57404743</v>
+      </c>
+      <c r="C38">
         <v>31369833</v>
       </c>
-      <c r="C38">
-        <v>30402467.56777352</v>
-      </c>
-      <c r="E38">
+      <c r="D38">
+        <v>32534714.675079554</v>
+      </c>
+      <c r="F38">
+        <v>-30333293</v>
+      </c>
+      <c r="G38">
         <v>-74814171</v>
       </c>
-      <c r="F38">
-        <v>32324644.75261209</v>
+      <c r="H38">
+        <v>34591701.86285506</v>
       </c>
     </row>
     <row r="39"/>
@@ -2851,44 +3171,50 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>-4425549</v>
+      </c>
+      <c r="C40">
         <v>-23060640</v>
       </c>
-      <c r="C40">
-        <v>-9975594.44985367</v>
-      </c>
-      <c r="E40">
+      <c r="D40">
+        <v>-10675222.937638167</v>
+      </c>
+      <c r="F40">
+        <v>-7074001</v>
+      </c>
+      <c r="G40">
         <v>7778203</v>
       </c>
-      <c r="F40">
-        <v>-14382824.156763043</v>
+      <c r="H40">
+        <v>-15391549.357596967</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>-4425549</v>
+      </c>
+      <c r="C42">
         <v>-23060640</v>
       </c>
-      <c r="C42">
-        <v>-9975594.44985367</v>
-      </c>
-      <c r="E42">
+      <c r="D42">
+        <v>-10675222.937638167</v>
+      </c>
+      <c r="F42">
+        <v>-7074001</v>
+      </c>
+      <c r="G42">
         <v>7778203</v>
       </c>
-      <c r="F42">
-        <v>-14382824.156763043</v>
+      <c r="H42">
+        <v>-15391549.357596967</v>
       </c>
     </row>
     <row r="43">
@@ -2896,16 +3222,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>-61830292</v>
+      </c>
+      <c r="C43">
         <v>8309193</v>
       </c>
-      <c r="C43">
-        <v>20426873.117919832</v>
-      </c>
-      <c r="E43">
+      <c r="D43">
+        <v>21859491.73744136</v>
+      </c>
+      <c r="F43">
+        <v>-37407294</v>
+      </c>
+      <c r="G43">
         <v>-67035968</v>
       </c>
-      <c r="F43">
-        <v>17941820.595849052</v>
+      <c r="H43">
+        <v>19200152.505258095</v>
       </c>
     </row>
     <row r="44">
@@ -2919,16 +3251,22 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>-61830292</v>
+      </c>
+      <c r="C46">
         <v>8309193</v>
       </c>
-      <c r="C46">
-        <v>20426873.117919832</v>
-      </c>
-      <c r="E46">
+      <c r="D46">
+        <v>21859491.73744136</v>
+      </c>
+      <c r="F46">
+        <v>-37407294</v>
+      </c>
+      <c r="G46">
         <v>-67035968</v>
       </c>
-      <c r="F46">
-        <v>17941820.595849052</v>
+      <c r="H46">
+        <v>19200152.505258095</v>
       </c>
     </row>
     <row r="47">
@@ -2938,7 +3276,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2947,16 +3291,22 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>-61830292</v>
+      </c>
+      <c r="C48">
         <v>8309193</v>
       </c>
-      <c r="C48">
-        <v>20426873.117919832</v>
-      </c>
-      <c r="E48">
+      <c r="D48">
+        <v>21859491.73744136</v>
+      </c>
+      <c r="F48">
+        <v>-37407294</v>
+      </c>
+      <c r="G48">
         <v>-67035968</v>
       </c>
-      <c r="F48">
-        <v>17941820.595849052</v>
+      <c r="H48">
+        <v>19200152.505258095</v>
       </c>
     </row>
     <row r="49"/>
@@ -2965,28 +3315,34 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>11397888</v>
+      </c>
+      <c r="C50">
         <v>10734557</v>
       </c>
-      <c r="C50">
-        <v>10922961.337121334</v>
-      </c>
-      <c r="E50">
+      <c r="D50">
+        <v>11689032.46810349</v>
+      </c>
+      <c r="F50">
+        <v>9323910</v>
+      </c>
+      <c r="G50">
         <v>8618763</v>
       </c>
-      <c r="F50">
-        <v>7608352.028975993</v>
+      <c r="H50">
+        <v>8141956.302016847</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2997,6 +3353,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3004,27 +3362,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3037,20 +3401,20 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
-      <c r="C3">
-        <v>278053116.3356527</v>
-      </c>
       <c r="D3">
-        <v>252492445.4122621</v>
-      </c>
-      <c r="F3">
-        <v>158071626.26964003</v>
+        <v>297554097.6840407</v>
+      </c>
+      <c r="E3">
+        <v>270200754.2903743</v>
       </c>
       <c r="H3">
-        <v>313299477.5294634</v>
-      </c>
-      <c r="I3">
-        <v>105062625.69251193</v>
+        <v>169157824.0300438</v>
+      </c>
+      <c r="J3">
+        <v>335272427.6919298</v>
+      </c>
+      <c r="K3">
+        <v>112431089.42722188</v>
       </c>
     </row>
     <row r="4">
@@ -3072,40 +3436,40 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="C7">
-        <v>-201355187.7931853</v>
-      </c>
       <c r="D7">
-        <v>-193274914.0714289</v>
-      </c>
-      <c r="F7">
-        <v>-105386171.06405188</v>
+        <v>-215477035.4937377</v>
+      </c>
+      <c r="E7">
+        <v>-206830059.73600188</v>
       </c>
       <c r="H7">
-        <v>-158785184.69221494</v>
-      </c>
-      <c r="I7">
-        <v>-82838737.2976283</v>
+        <v>-112777326.33460544</v>
+      </c>
+      <c r="J7">
+        <v>-169921427.1695167</v>
+      </c>
+      <c r="K7">
+        <v>-88648550.51696652</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
-      <c r="C8">
-        <v>76697928.54246742</v>
-      </c>
       <c r="D8">
-        <v>59217531.34083323</v>
-      </c>
-      <c r="F8">
-        <v>52685455.20558814</v>
+        <v>82077062.190303</v>
+      </c>
+      <c r="E8">
+        <v>63370694.55437245</v>
       </c>
       <c r="H8">
-        <v>154514292.83724853</v>
-      </c>
-      <c r="I8">
-        <v>22223888.39488361</v>
+        <v>56380497.69543837</v>
+      </c>
+      <c r="J8">
+        <v>165351000.52241316</v>
+      </c>
+      <c r="K8">
+        <v>23782538.910255343</v>
       </c>
     </row>
     <row r="9">
@@ -3132,20 +3496,20 @@
       <c r="A13" t="str">
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
-      <c r="C13">
-        <v>76697928.54246742</v>
-      </c>
       <c r="D13">
-        <v>59217531.34083323</v>
-      </c>
-      <c r="F13">
-        <v>52685455.20558814</v>
+        <v>82077062.190303</v>
+      </c>
+      <c r="E13">
+        <v>63370694.55437245</v>
       </c>
       <c r="H13">
-        <v>154514292.83724853</v>
-      </c>
-      <c r="I13">
-        <v>22223888.39488361</v>
+        <v>56380497.69543837</v>
+      </c>
+      <c r="J13">
+        <v>165351000.52241316</v>
+      </c>
+      <c r="K13">
+        <v>23782538.910255343</v>
       </c>
     </row>
     <row r="14"/>
@@ -3153,40 +3517,40 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
-      <c r="C15">
-        <v>-26126545.84120642</v>
-      </c>
       <c r="D15">
-        <v>-26186373.79717132</v>
-      </c>
-      <c r="F15">
-        <v>-25333128.344008174</v>
+        <v>-27958905.391286537</v>
+      </c>
+      <c r="E15">
+        <v>-28022929.321994536</v>
       </c>
       <c r="H15">
-        <v>-12226911.341943799</v>
-      </c>
-      <c r="I15">
-        <v>-5303564.37007383</v>
+        <v>-27109842.33967677</v>
+      </c>
+      <c r="J15">
+        <v>-13084433.721731875</v>
+      </c>
+      <c r="K15">
+        <v>-5675524.631565507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
-      <c r="C16">
-        <v>-36402457.43289877</v>
-      </c>
       <c r="D16">
-        <v>-36584964.75472025</v>
-      </c>
-      <c r="F16">
-        <v>-30341752.087493278</v>
+        <v>-38955507.91760367</v>
+      </c>
+      <c r="E16">
+        <v>-39150815.21061659</v>
       </c>
       <c r="H16">
-        <v>-25112231.394699488</v>
-      </c>
-      <c r="I16">
-        <v>-214011.85550691668</v>
+        <v>-32469740.974412832</v>
+      </c>
+      <c r="J16">
+        <v>-26873453.000478145</v>
+      </c>
+      <c r="K16">
+        <v>-229021.36612695342</v>
       </c>
     </row>
     <row r="17">
@@ -3198,37 +3562,37 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
-      <c r="C18">
-        <v>4193117.474641919</v>
-      </c>
       <c r="D18">
-        <v>6150939.30897583</v>
-      </c>
-      <c r="F18">
-        <v>24479460.5391776</v>
-      </c>
-      <c r="I18">
-        <v>259280.8778873967</v>
+        <v>4487197.637246114</v>
+      </c>
+      <c r="E18">
+        <v>6582329.376888635</v>
+      </c>
+      <c r="H18">
+        <v>26196303.384473532</v>
+      </c>
+      <c r="K18">
+        <v>277465.286788508</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
-      <c r="C19">
-        <v>-798453.0284614968</v>
-      </c>
       <c r="D19">
-        <v>-10320044.996526081</v>
-      </c>
-      <c r="F19">
-        <v>-19797634.631554384</v>
+        <v>-854451.7448966524</v>
+      </c>
+      <c r="E19">
+        <v>-11043831.184014225</v>
       </c>
       <c r="H19">
-        <v>-20160407.13330284</v>
-      </c>
-      <c r="I19">
-        <v>-714951.0644804913</v>
+        <v>-21186122.22982353</v>
+      </c>
+      <c r="J19">
+        <v>-21574337.42354227</v>
+      </c>
+      <c r="K19">
+        <v>-765093.4529463475</v>
       </c>
     </row>
     <row r="20">
@@ -3240,20 +3604,20 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
-      <c r="C21">
-        <v>17563589.714542653</v>
-      </c>
       <c r="D21">
-        <v>-7722912.898608573</v>
-      </c>
-      <c r="F21">
-        <v>1692400.6817099096</v>
+        <v>18795394.773762263</v>
+      </c>
+      <c r="E21">
+        <v>-8264551.785364255</v>
       </c>
       <c r="H21">
-        <v>97014742.9673024</v>
-      </c>
-      <c r="I21">
-        <v>16250641.982709773</v>
+        <v>1811095.5359987707</v>
+      </c>
+      <c r="J21">
+        <v>103818776.37666087</v>
+      </c>
+      <c r="K21">
+        <v>17390364.74640505</v>
       </c>
     </row>
     <row r="22"/>
@@ -3271,27 +3635,27 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>0</v>
       </c>
-      <c r="F25">
-        <v>24894100.664947763</v>
-      </c>
       <c r="H25">
-        <v>26621147.897292126</v>
-      </c>
-      <c r="I25">
-        <v>814089.0866293263</v>
+        <v>26640023.886919554</v>
+      </c>
+      <c r="J25">
+        <v>28488195.875244267</v>
+      </c>
+      <c r="K25">
+        <v>871184.4225978702</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="C26">
-        <v>-1762994.9565351023</v>
-      </c>
-      <c r="F26">
+      <c r="D26">
+        <v>-1886640.8707322697</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
@@ -3329,20 +3693,20 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
-      <c r="C33">
-        <v>15800594.758007552</v>
-      </c>
       <c r="D33">
-        <v>17171187.76633919</v>
-      </c>
-      <c r="F33">
-        <v>26586501.346657675</v>
+        <v>16908753.903029993</v>
+      </c>
+      <c r="E33">
+        <v>18375472.101555295</v>
       </c>
       <c r="H33">
-        <v>123635890.86459453</v>
-      </c>
-      <c r="I33">
-        <v>17064731.0693391</v>
+        <v>28451119.422918327</v>
+      </c>
+      <c r="J33">
+        <v>132306972.25190516</v>
+      </c>
+      <c r="K33">
+        <v>18261549.16900292</v>
       </c>
     </row>
     <row r="34"/>
@@ -3350,40 +3714,40 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="C35">
-        <v>19475225.278795175</v>
-      </c>
       <c r="D35">
-        <v>7684635.973849313</v>
-      </c>
-      <c r="F35">
-        <v>37762537.26051903</v>
+        <v>20841101.01477858</v>
+      </c>
+      <c r="E35">
+        <v>8223590.346201267</v>
       </c>
       <c r="H35">
-        <v>33284241.340607386</v>
-      </c>
-      <c r="I35">
-        <v>8244887.548387096</v>
+        <v>40410975.60384704</v>
+      </c>
+      <c r="J35">
+        <v>35618598.81205862</v>
+      </c>
+      <c r="K35">
+        <v>8823134.612903226</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
-      <c r="C36">
-        <v>-172630218.68595594</v>
-      </c>
       <c r="D36">
-        <v>-160288045.20450315</v>
-      </c>
-      <c r="F36">
-        <v>-75585463.48184764</v>
+        <v>-184737468.9808929</v>
+      </c>
+      <c r="E36">
+        <v>-171529689.32306537</v>
       </c>
       <c r="H36">
-        <v>-27964172.914582357</v>
-      </c>
-      <c r="I36">
-        <v>-12653739.62279863</v>
+        <v>-80886575.4887688</v>
+      </c>
+      <c r="J36">
+        <v>-29925412.628839225</v>
+      </c>
+      <c r="K36">
+        <v>-13541197.183510434</v>
       </c>
     </row>
     <row r="37">
@@ -3395,20 +3759,20 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
-      <c r="C38">
-        <v>-137354398.6491532</v>
-      </c>
       <c r="D38">
-        <v>-135432221.46431464</v>
-      </c>
-      <c r="F38">
-        <v>-11236424.874670947</v>
+        <v>-146987614.0630843</v>
+      </c>
+      <c r="E38">
+        <v>-144930626.8753088</v>
       </c>
       <c r="H38">
-        <v>128955959.29061957</v>
-      </c>
-      <c r="I38">
-        <v>12655878.994927566</v>
+        <v>-12024480.462003434</v>
+      </c>
+      <c r="J38">
+        <v>138000158.43512455</v>
+      </c>
+      <c r="K38">
+        <v>13543486.59839571</v>
       </c>
     </row>
     <row r="39"/>
@@ -3416,71 +3780,71 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="C40">
-        <v>3692207.562061203</v>
-      </c>
       <c r="D40">
-        <v>-715022.1448481698</v>
-      </c>
-      <c r="F40">
-        <v>20004846.302868348</v>
+        <v>3951156.901493226</v>
+      </c>
+      <c r="E40">
+        <v>-765169.5184655748</v>
       </c>
       <c r="H40">
-        <v>-12750382.284970986</v>
-      </c>
-      <c r="I40">
-        <v>-6906361.758150641</v>
+        <v>21407866.487539385</v>
+      </c>
+      <c r="J40">
+        <v>-13644617.783572208</v>
+      </c>
+      <c r="K40">
+        <v>-7390732.635218372</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="H41">
-        <v>-35695070.28016583</v>
-      </c>
-      <c r="I41">
-        <v>-2968228.9695000625</v>
+      <c r="J41">
+        <v>-38198508.86390257</v>
+      </c>
+      <c r="K41">
+        <v>-3176402.783679119</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
-      <c r="C42">
-        <v>3692207.562061203</v>
-      </c>
       <c r="D42">
-        <v>-715022.1448481698</v>
-      </c>
-      <c r="F42">
-        <v>20004846.302868348</v>
+        <v>3951156.901493226</v>
+      </c>
+      <c r="E42">
+        <v>-765169.5184655748</v>
       </c>
       <c r="H42">
-        <v>22944687.99519485</v>
-      </c>
-      <c r="I42">
-        <v>-3938132.788650578</v>
+        <v>21407866.487539385</v>
+      </c>
+      <c r="J42">
+        <v>24553891.080330364</v>
+      </c>
+      <c r="K42">
+        <v>-4214329.851539252</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
-      <c r="C43">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D43">
-        <v>-136147243.6091628</v>
-      </c>
-      <c r="F43">
-        <v>8768421.4281974</v>
+        <v>-143036457.16159108</v>
+      </c>
+      <c r="E43">
+        <v>-145695796.39377436</v>
       </c>
       <c r="H43">
-        <v>116205577.00564857</v>
-      </c>
-      <c r="I43">
-        <v>5749517.236776926</v>
+        <v>9383386.025535949</v>
+      </c>
+      <c r="J43">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K43">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="44">
@@ -3493,30 +3857,30 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
-      <c r="C46">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D46">
-        <v>-136147243.6091628</v>
-      </c>
-      <c r="F46">
-        <v>8768421.4281974</v>
+        <v>-143036457.16159108</v>
+      </c>
+      <c r="E46">
+        <v>-145695796.39377436</v>
       </c>
       <c r="H46">
-        <v>116205577.00564857</v>
-      </c>
-      <c r="I46">
-        <v>5749517.236776926</v>
+        <v>9383386.025535949</v>
+      </c>
+      <c r="J46">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K46">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -3524,20 +3888,20 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
-      <c r="C48">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D48">
-        <v>-136147243.6091628</v>
-      </c>
-      <c r="F48">
-        <v>8768421.4281974</v>
+        <v>-143036457.16159108</v>
+      </c>
+      <c r="E48">
+        <v>-145695796.39377436</v>
       </c>
       <c r="H48">
-        <v>116205577.00564857</v>
-      </c>
-      <c r="I48">
-        <v>5749517.236776926</v>
+        <v>9383386.025535949</v>
+      </c>
+      <c r="J48">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K48">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="49"/>
@@ -3545,32 +3909,32 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
-      <c r="C50">
-        <v>42939214.156960845</v>
-      </c>
       <c r="D50">
-        <v>39624604.8488155</v>
-      </c>
-      <c r="F50">
-        <v>41219091.64317405</v>
+        <v>45950713.63383962</v>
+      </c>
+      <c r="E50">
+        <v>42403637.46775298</v>
       </c>
       <c r="H50">
-        <v>20612617.34768741</v>
-      </c>
-      <c r="I50">
-        <v>12490219.4759</v>
+        <v>44109952.02238558</v>
+      </c>
+      <c r="J50">
+        <v>22058262.955749847</v>
+      </c>
+      <c r="K50">
+        <v>13366208.712225517</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3581,6 +3945,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3588,27 +3954,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3622,28 +3994,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>-482736862</v>
+      </c>
+      <c r="C3">
         <v>-916243797</v>
       </c>
-      <c r="C3">
-        <v>698880825.0122173</v>
-      </c>
       <c r="D3">
-        <v>82589523.98573898</v>
+        <v>747896143.0669775</v>
       </c>
       <c r="E3">
+        <v>88381858.87499778</v>
+      </c>
+      <c r="F3">
+        <v>127860174</v>
+      </c>
+      <c r="G3">
         <v>146038809</v>
       </c>
-      <c r="F3">
-        <v>-23323163.467789076</v>
-      </c>
-      <c r="G3">
-        <v>-86657002.08792417</v>
-      </c>
       <c r="H3">
-        <v>19466689.021406382</v>
+        <v>-24958910.557283</v>
       </c>
       <c r="I3">
-        <v>-47683820.01036463</v>
+        <v>-92734605.54619242</v>
+      </c>
+      <c r="J3">
+        <v>20831966.075388603</v>
+      </c>
+      <c r="K3">
+        <v>-51028077.74391041</v>
       </c>
     </row>
     <row r="4">
@@ -3651,28 +4029,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>-53521099</v>
+      </c>
+      <c r="C4">
         <v>8309193</v>
       </c>
-      <c r="C4">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D4">
-        <v>-154089064.20501184</v>
+        <v>-143036457.16159108</v>
       </c>
       <c r="E4">
+        <v>-164895948.89903244</v>
+      </c>
+      <c r="F4">
+        <v>-104443262</v>
+      </c>
+      <c r="G4">
         <v>-67035968</v>
       </c>
-      <c r="F4">
-        <v>8768421.4281974</v>
-      </c>
-      <c r="G4">
-        <v>-9173399.167651653</v>
-      </c>
       <c r="H4">
-        <v>116205577.00564857</v>
+        <v>9383386.025535949</v>
       </c>
       <c r="I4">
-        <v>5749517.236776926</v>
+        <v>-9816766.479722146</v>
+      </c>
+      <c r="J4">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K4">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="5">
@@ -3680,28 +4064,34 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-14833686</v>
+      </c>
+      <c r="C5">
         <v>-23946736</v>
       </c>
-      <c r="C5">
-        <v>209810106.68462977</v>
-      </c>
       <c r="D5">
-        <v>143490549.2224268</v>
+        <v>224524931.7909997</v>
       </c>
       <c r="E5">
+        <v>153554117.51086357</v>
+      </c>
+      <c r="F5">
+        <v>99186039</v>
+      </c>
+      <c r="G5">
         <v>40038584</v>
       </c>
-      <c r="F5">
-        <v>59780611.19096039</v>
-      </c>
-      <c r="G5">
-        <v>25197607.615671087</v>
-      </c>
       <c r="H5">
-        <v>134767612.48366308</v>
+        <v>63973265.45498554</v>
       </c>
       <c r="I5">
-        <v>34066912.777169295</v>
+        <v>26964816.998586375</v>
+      </c>
+      <c r="J5">
+        <v>144219406.19863865</v>
+      </c>
+      <c r="K5">
+        <v>36456162.13865741</v>
       </c>
     </row>
     <row r="6">
@@ -3709,38 +4099,44 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>22132445</v>
+      </c>
+      <c r="C6">
         <v>10734557</v>
       </c>
-      <c r="C6">
-        <v>42939214.156960845</v>
-      </c>
       <c r="D6">
-        <v>32016252.81983951</v>
+        <v>45950713.63383962</v>
       </c>
       <c r="E6">
+        <v>34261681.16573613</v>
+      </c>
+      <c r="F6">
+        <v>17942673</v>
+      </c>
+      <c r="G6">
         <v>8618763</v>
       </c>
-      <c r="F6">
-        <v>41219091.64317405</v>
-      </c>
-      <c r="G6">
-        <v>33610739.61419806</v>
-      </c>
       <c r="H6">
-        <v>20612617.34768741</v>
+        <v>44109952.02238558</v>
       </c>
       <c r="I6">
-        <v>12490219.4759</v>
+        <v>35967995.720368735</v>
+      </c>
+      <c r="J6">
+        <v>22058262.955749847</v>
+      </c>
+      <c r="K6">
+        <v>13366208.712225517</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>0</v>
       </c>
     </row>
@@ -3749,28 +4145,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>533214</v>
+      </c>
+      <c r="C8">
         <v>-873941</v>
       </c>
-      <c r="C8">
-        <v>1746134.2900107289</v>
-      </c>
       <c r="D8">
-        <v>329397.85202630056</v>
+        <v>1868597.6979740288</v>
       </c>
       <c r="E8">
+        <v>352499.8458223698</v>
+      </c>
+      <c r="F8">
+        <v>282025</v>
+      </c>
+      <c r="G8">
         <v>301232</v>
       </c>
-      <c r="F8">
-        <v>1261960.6962636637</v>
-      </c>
-      <c r="G8">
-        <v>858425.6505188256</v>
-      </c>
       <c r="H8">
-        <v>203693.94966767836</v>
+        <v>1350467.06628589</v>
       </c>
       <c r="I8">
-        <v>79255.52668967278</v>
+        <v>918630.4877109308</v>
+      </c>
+      <c r="J8">
+        <v>217979.8241279156</v>
+      </c>
+      <c r="K8">
+        <v>84814.03496356045</v>
       </c>
     </row>
     <row r="9">
@@ -3793,28 +4195,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-109318015</v>
+      </c>
+      <c r="C12">
         <v>-58804925</v>
       </c>
-      <c r="C12">
-        <v>117079859.81185986</v>
-      </c>
       <c r="D12">
-        <v>85059007.09074548</v>
+        <v>125291140.42094615</v>
       </c>
       <c r="E12">
+        <v>91024536.74439153</v>
+      </c>
+      <c r="F12">
+        <v>55067820</v>
+      </c>
+      <c r="G12">
         <v>23816471</v>
       </c>
-      <c r="F12">
-        <v>50697639.62422628</v>
-      </c>
-      <c r="G12">
-        <v>23488617.904324636</v>
-      </c>
       <c r="H12">
-        <v>27629227.393873878</v>
+        <v>54253268.62687294</v>
       </c>
       <c r="I12">
-        <v>11708774.474890266</v>
+        <v>25135968.977702677</v>
+      </c>
+      <c r="J12">
+        <v>29566976.034057774</v>
+      </c>
+      <c r="K12">
+        <v>12529957.836027943</v>
       </c>
     </row>
     <row r="13">
@@ -3832,28 +4240,34 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>44332481</v>
+      </c>
+      <c r="C15">
         <v>2253377</v>
       </c>
-      <c r="C15">
-        <v>19081782.582816098</v>
-      </c>
       <c r="D15">
-        <v>12389594.343226757</v>
+        <v>20420064.60297621</v>
       </c>
       <c r="E15">
+        <v>13258526.335018206</v>
+      </c>
+      <c r="F15">
+        <v>8574384</v>
+      </c>
+      <c r="G15">
         <v>5238464</v>
       </c>
-      <c r="F15">
-        <v>13035699.645501968</v>
-      </c>
-      <c r="G15">
-        <v>15990173.713098638</v>
-      </c>
       <c r="H15">
-        <v>94327624.96917932</v>
+        <v>13949945.596060755</v>
       </c>
       <c r="I15">
-        <v>45802046.42964819</v>
+        <v>17111628.791344196</v>
+      </c>
+      <c r="J15">
+        <v>100943200.00535755</v>
+      </c>
+      <c r="K15">
+        <v>49014327.82722246</v>
       </c>
     </row>
     <row r="16">
@@ -3870,11 +4284,11 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>1762994.9565351023</v>
-      </c>
-      <c r="F18">
-        <v>-24894100.664947763</v>
+      <c r="D18">
+        <v>1886640.8707322697</v>
+      </c>
+      <c r="H18">
+        <v>-26640023.886919554</v>
       </c>
     </row>
     <row r="19">
@@ -3887,28 +4301,34 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>27486189</v>
+      </c>
+      <c r="C20">
         <v>22744196</v>
       </c>
-      <c r="C20">
-        <v>27200120.886447135</v>
-      </c>
       <c r="D20">
-        <v>13696297.116588758</v>
+        <v>29107774.564531416</v>
       </c>
       <c r="E20">
+        <v>14656873.419895345</v>
+      </c>
+      <c r="F20">
+        <v>17319137</v>
+      </c>
+      <c r="G20">
         <v>2063654</v>
       </c>
-      <c r="F20">
-        <v>-21539679.753257804</v>
-      </c>
-      <c r="G20">
-        <v>-48750349.26646908</v>
-      </c>
       <c r="H20">
-        <v>43878646.38607516</v>
+        <v>-23050343.969700076</v>
       </c>
       <c r="I20">
-        <v>27195192.081628166</v>
+        <v>-52169406.97854017</v>
+      </c>
+      <c r="J20">
+        <v>46956032.016720034</v>
+      </c>
+      <c r="K20">
+        <v>29102500.082842823</v>
       </c>
     </row>
     <row r="21">
@@ -3925,11 +4345,11 @@
       <c r="A23" t="str">
         <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="H23">
-        <v>-26621147.897292126</v>
-      </c>
-      <c r="I23">
-        <v>-681371.0753262334</v>
+      <c r="J23">
+        <v>-28488195.875244267</v>
+      </c>
+      <c r="K23">
+        <v>-729158.3643391284</v>
       </c>
     </row>
     <row r="24">
@@ -3957,38 +4377,44 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>-414382077</v>
+      </c>
+      <c r="C28">
         <v>-900606254</v>
       </c>
-      <c r="C28">
-        <v>623356160.9486009</v>
-      </c>
       <c r="D28">
-        <v>93188038.96832402</v>
+        <v>667074631.103732</v>
       </c>
       <c r="E28">
+        <v>99723690.26316667</v>
+      </c>
+      <c r="F28">
+        <v>133117397</v>
+      </c>
+      <c r="G28">
         <v>173036193</v>
       </c>
-      <c r="F28">
-        <v>-91442711.2678329</v>
-      </c>
-      <c r="G28">
-        <v>-102681210.5359436</v>
-      </c>
       <c r="H28">
-        <v>-231506500.46790525</v>
+        <v>-97855955.72407347</v>
       </c>
       <c r="I28">
-        <v>-87500250.02431086</v>
+        <v>-109882656.06505665</v>
+      </c>
+      <c r="J28">
+        <v>-247742980.77480236</v>
+      </c>
+      <c r="K28">
+        <v>-93636993.84574518</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>-534129977</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0</v>
       </c>
     </row>
@@ -4002,28 +4428,34 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>-150113553</v>
+      </c>
+      <c r="C31">
         <v>-181447862</v>
       </c>
-      <c r="C31">
-        <v>558247927.9697257</v>
-      </c>
       <c r="D31">
-        <v>102859540.92564787</v>
+        <v>597400096.3560435</v>
       </c>
       <c r="E31">
+        <v>110073493.48093385</v>
+      </c>
+      <c r="F31">
+        <v>115775237</v>
+      </c>
+      <c r="G31">
         <v>181421803</v>
       </c>
-      <c r="F31">
-        <v>-122393597.57487328</v>
-      </c>
-      <c r="G31">
-        <v>-126617906.89892553</v>
-      </c>
       <c r="H31">
-        <v>-324571987.74884325</v>
+        <v>-130977551.94634123</v>
       </c>
       <c r="I31">
-        <v>-121659131.68771864</v>
+        <v>-135498129.04262272</v>
+      </c>
+      <c r="J31">
+        <v>-347335524.3087384</v>
+      </c>
+      <c r="K31">
+        <v>-130191575.01786044</v>
       </c>
     </row>
     <row r="32">
@@ -4036,28 +4468,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-2892666</v>
+      </c>
+      <c r="C33">
         <v>-2852763</v>
       </c>
-      <c r="C33">
-        <v>-203764.0490570226</v>
-      </c>
       <c r="D33">
-        <v>-42711.65161765492</v>
+        <v>-218054.8398688626</v>
       </c>
       <c r="E33">
+        <v>-45707.191220056906</v>
+      </c>
+      <c r="F33">
+        <v>-37163</v>
+      </c>
+      <c r="G33">
         <v>-32999</v>
       </c>
-      <c r="F33">
-        <v>3217404.062000017</v>
-      </c>
-      <c r="G33">
-        <v>3357521.202701338</v>
-      </c>
       <c r="H33">
-        <v>-3134192.8007198814</v>
+        <v>3443053.5257792696</v>
       </c>
       <c r="I33">
-        <v>-333744.34880999755</v>
+        <v>3592997.64408622</v>
+      </c>
+      <c r="J33">
+        <v>-3354006.3246773304</v>
+      </c>
+      <c r="K33">
+        <v>-357151.1798753869</v>
       </c>
     </row>
     <row r="34">
@@ -4080,28 +4518,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-56275248</v>
+      </c>
+      <c r="C37">
         <v>-22729342</v>
       </c>
-      <c r="C37">
-        <v>-10797760.33488433</v>
-      </c>
       <c r="D37">
-        <v>-15427726.694157198</v>
+        <v>-11555050.616935177</v>
       </c>
       <c r="E37">
+        <v>-16509735.104908502</v>
+      </c>
+      <c r="F37">
+        <v>-5170216</v>
+      </c>
+      <c r="G37">
         <v>-6696267</v>
       </c>
-      <c r="F37">
-        <v>6999860.536974902</v>
-      </c>
-      <c r="G37">
-        <v>11325021.871935898</v>
-      </c>
       <c r="H37">
-        <v>-19180191.150052566</v>
+        <v>7490788.8587711</v>
       </c>
       <c r="I37">
-        <v>-5788299.241896876</v>
+        <v>12119291.122376917</v>
+      </c>
+      <c r="J37">
+        <v>-20525374.95811382</v>
+      </c>
+      <c r="K37">
+        <v>-6194255.906014457</v>
       </c>
     </row>
     <row r="38">
@@ -4114,28 +4558,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>14248469</v>
+      </c>
+      <c r="C39">
         <v>25698615</v>
       </c>
-      <c r="C39">
-        <v>-35490427.64465959</v>
-      </c>
       <c r="D39">
-        <v>-2304808.8684731023</v>
+        <v>-37979513.81878955</v>
       </c>
       <c r="E39">
+        <v>-2466454.367534643</v>
+      </c>
+      <c r="F39">
+        <v>-859603</v>
+      </c>
+      <c r="G39">
         <v>-3798597</v>
       </c>
-      <c r="F39">
-        <v>-5159863.548065239</v>
-      </c>
-      <c r="G39">
-        <v>-9106623.885888062</v>
-      </c>
       <c r="H39">
-        <v>-250897.93825173288</v>
+        <v>-5521745.493993803</v>
       </c>
       <c r="I39">
-        <v>-943571.0535634737</v>
+        <v>-9745307.97936577</v>
+      </c>
+      <c r="J39">
+        <v>-268494.4179412097</v>
+      </c>
+      <c r="K39">
+        <v>-1009747.479704326</v>
       </c>
     </row>
     <row r="40">
@@ -4143,28 +4593,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>-11879788</v>
+      </c>
+      <c r="C40">
         <v>4238670</v>
       </c>
-      <c r="C40">
-        <v>3218464.868848307</v>
-      </c>
       <c r="D40">
-        <v>4403240.098247219</v>
+        <v>3444188.731270651</v>
       </c>
       <c r="E40">
+        <v>4712057.004024092</v>
+      </c>
+      <c r="F40">
+        <v>25331769</v>
+      </c>
+      <c r="G40">
         <v>7777794</v>
       </c>
-      <c r="F40">
-        <v>18406219.18587199</v>
-      </c>
-      <c r="G40">
-        <v>15029862.043917535</v>
-      </c>
       <c r="H40">
-        <v>-4210294.684879515</v>
+        <v>19697121.232820228</v>
       </c>
       <c r="I40">
-        <v>10893978.005957436</v>
+        <v>16083966.609440431</v>
+      </c>
+      <c r="J40">
+        <v>-4505579.554199014</v>
+      </c>
+      <c r="K40">
+        <v>11658016.419565696</v>
       </c>
     </row>
     <row r="41">
@@ -4177,28 +4633,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>583197</v>
+      </c>
+      <c r="C42">
         <v>1527322</v>
       </c>
-      <c r="C42">
-        <v>-517580.20609185885</v>
-      </c>
       <c r="D42">
-        <v>5297867.416165264</v>
+        <v>-553880.1838741901</v>
       </c>
       <c r="E42">
+        <v>5669428.127407773</v>
+      </c>
+      <c r="F42">
+        <v>2668614</v>
+      </c>
+      <c r="G42">
         <v>1898493</v>
       </c>
-      <c r="F42">
-        <v>891329.7492109839</v>
-      </c>
-      <c r="G42">
-        <v>1637665.8235695914</v>
-      </c>
       <c r="H42">
-        <v>333479.0804461841</v>
+        <v>953842.282944446</v>
       </c>
       <c r="I42">
-        <v>51479.28779824306</v>
+        <v>1752521.9025130523</v>
+      </c>
+      <c r="J42">
+        <v>356867.3071762463</v>
+      </c>
+      <c r="K42">
+        <v>55089.736925416226</v>
       </c>
     </row>
     <row r="43">
@@ -4211,28 +4673,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-94175506</v>
+      </c>
+      <c r="C44">
         <v>-92439508</v>
       </c>
-      <c r="C44">
-        <v>111695822.68712844</v>
-      </c>
       <c r="D44">
-        <v>-3308167.5068572885</v>
+        <v>119529499.15736498</v>
       </c>
       <c r="E44">
+        <v>-3540182.575412358</v>
+      </c>
+      <c r="F44">
+        <v>-3656602</v>
+      </c>
+      <c r="G44">
         <v>-5414744</v>
       </c>
-      <c r="F44">
-        <v>12874858.658607177</v>
-      </c>
-      <c r="G44">
-        <v>4207999.137436817</v>
-      </c>
       <c r="H44">
-        <v>123573627.44171154</v>
+        <v>13777824.185026769</v>
       </c>
       <c r="I44">
-        <v>29318424.180897</v>
+        <v>4503123.010798226</v>
+      </c>
+      <c r="J44">
+        <v>132240342.04520643</v>
+      </c>
+      <c r="K44">
+        <v>31374642.973372698</v>
       </c>
     </row>
     <row r="45">
@@ -4250,28 +4718,34 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>-2252</v>
+      </c>
+      <c r="C47">
         <v>257028</v>
       </c>
-      <c r="C47">
-        <v>-1128909.7676123476</v>
-      </c>
       <c r="D47">
-        <v>-1402287.8071227898</v>
+        <v>-1208084.741848731</v>
       </c>
       <c r="E47">
+        <v>-1500635.8808007794</v>
+      </c>
+      <c r="F47">
+        <v>-691264</v>
+      </c>
+      <c r="G47">
         <v>1136</v>
       </c>
-      <c r="F47">
-        <v>-332264.73256551893</v>
-      </c>
-      <c r="G47">
-        <v>-402757.7606215216</v>
-      </c>
       <c r="H47">
-        <v>-2324902.659944999</v>
+        <v>-355567.79220346804</v>
       </c>
       <c r="I47">
-        <v>2680699.881736269</v>
+        <v>-431004.7793253783</v>
+      </c>
+      <c r="J47">
+        <v>-2487957.4172730027</v>
+      </c>
+      <c r="K47">
+        <v>2868708.126647502</v>
       </c>
     </row>
     <row r="48">
@@ -4279,28 +4753,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-113874730</v>
+      </c>
+      <c r="C48">
         <v>-98728437</v>
       </c>
-      <c r="C48">
-        <v>-1667612.5747964494</v>
-      </c>
       <c r="D48">
-        <v>3113093.056491705</v>
+        <v>-1784568.9396306637</v>
       </c>
       <c r="E48">
+        <v>3331426.770677295</v>
+      </c>
+      <c r="F48">
+        <v>-243375</v>
+      </c>
+      <c r="G48">
         <v>-2120426</v>
       </c>
-      <c r="F48">
-        <v>-5946657.6049939245</v>
-      </c>
-      <c r="G48">
-        <v>-2111992.0700696716</v>
-      </c>
       <c r="H48">
-        <v>-1741140.007371066</v>
+        <v>-6363720.576876778</v>
       </c>
       <c r="I48">
-        <v>-1720085.048710806</v>
+        <v>-2260114.552957633</v>
+      </c>
+      <c r="J48">
+        <v>-1863253.1462423012</v>
+      </c>
+      <c r="K48">
+        <v>-1840721.5188018607</v>
       </c>
     </row>
     <row r="49">
@@ -4308,16 +4788,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>-482736862</v>
+      </c>
+      <c r="C49">
         <v>-916243797</v>
       </c>
-      <c r="C49">
-        <v>699504076.5461386</v>
-      </c>
-      <c r="E49">
+      <c r="D49">
+        <v>748563105.7331406</v>
+      </c>
+      <c r="F49">
+        <v>127860174</v>
+      </c>
+      <c r="G49">
         <v>146038809</v>
       </c>
-      <c r="F49">
-        <v>-22893678.648675106</v>
+      <c r="H49">
+        <v>-24499304.243551984</v>
       </c>
     </row>
     <row r="50">
@@ -4344,11 +4830,11 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="H54">
-        <v>-37152.499456524965</v>
-      </c>
-      <c r="I54">
-        <v>-63977.906290649255</v>
+      <c r="J54">
+        <v>-39758.15339954028</v>
+      </c>
+      <c r="K54">
+        <v>-68464.93371089504</v>
       </c>
     </row>
     <row r="55">
@@ -4390,17 +4876,17 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-623251.533921289</v>
-      </c>
-      <c r="F62">
-        <v>-429484.81911396835</v>
+      <c r="D62">
+        <v>-666962.6661629486</v>
       </c>
       <c r="H62">
-        <v>-162754.1988524658</v>
-      </c>
-      <c r="I62">
-        <v>-54776.19460563907</v>
+        <v>-459606.31373101455</v>
+      </c>
+      <c r="J62">
+        <v>-174168.804227226</v>
+      </c>
+      <c r="K62">
+        <v>-58617.86904330576</v>
       </c>
     </row>
     <row r="63">
@@ -4424,28 +4910,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-604472611</v>
+      </c>
+      <c r="C67">
         <v>-10721482</v>
       </c>
-      <c r="C67">
-        <v>-6075175.895255089</v>
-      </c>
       <c r="D67">
-        <v>-4968183.625513035</v>
+        <v>-6501252.370796302</v>
       </c>
       <c r="E67">
+        <v>-5316622.288935681</v>
+      </c>
+      <c r="F67">
+        <v>-2702286</v>
+      </c>
+      <c r="G67">
         <v>-2110408</v>
       </c>
-      <c r="F67">
-        <v>-8102682.599242431</v>
-      </c>
-      <c r="G67">
-        <v>5014561.951960371</v>
-      </c>
       <c r="H67">
-        <v>-14279389.13399184</v>
+        <v>-8670956.259764876</v>
       </c>
       <c r="I67">
-        <v>-27885822.286034174</v>
+        <v>5366253.313611823</v>
+      </c>
+      <c r="J67">
+        <v>-15280860.021418264</v>
+      </c>
+      <c r="K67">
+        <v>-29841566.956156712</v>
       </c>
     </row>
     <row r="68">
@@ -4497,17 +4989,17 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>0</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>0</v>
       </c>
-      <c r="H77">
-        <v>1411339.085233516</v>
-      </c>
-      <c r="I77">
-        <v>1062809.7572715771</v>
+      <c r="J77">
+        <v>1510321.9613835749</v>
+      </c>
+      <c r="K77">
+        <v>1137348.8724110692</v>
       </c>
     </row>
     <row r="78">
@@ -4518,25 +5010,31 @@
         <v>-10721482</v>
       </c>
       <c r="C78">
-        <v>-6075175.895255089</v>
+        <v>-10721482</v>
       </c>
       <c r="D78">
-        <v>-4968183.625513035</v>
+        <v>-6501252.370796302</v>
       </c>
       <c r="E78">
+        <v>-5316622.288935681</v>
+      </c>
+      <c r="F78">
+        <v>-2702286</v>
+      </c>
+      <c r="G78">
         <v>-2110408</v>
       </c>
-      <c r="F78">
-        <v>-8102682.599242431</v>
-      </c>
-      <c r="G78">
-        <v>5014561.951960371</v>
-      </c>
       <c r="H78">
-        <v>-15690728.219225354</v>
+        <v>-8670956.259764876</v>
       </c>
       <c r="I78">
-        <v>-28948632.043305755</v>
+        <v>5366253.313611823</v>
+      </c>
+      <c r="J78">
+        <v>-16791181.98280184</v>
+      </c>
+      <c r="K78">
+        <v>-30978915.828567784</v>
       </c>
     </row>
     <row r="79">
@@ -4618,10 +5116,10 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="B94">
+      <c r="C94">
         <v>0</v>
       </c>
-      <c r="E94">
+      <c r="G94">
         <v>0</v>
       </c>
     </row>
@@ -4644,11 +5142,17 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="G98">
-        <v>73058722.20593843</v>
-      </c>
-      <c r="H98">
-        <v>-46674949.30208302</v>
+      <c r="B98">
+        <v>-593751129</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>78182623.70307258</v>
+      </c>
+      <c r="J98">
+        <v>-49948450.88254406</v>
       </c>
     </row>
     <row r="99">
@@ -4662,22 +5166,28 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>666978391</v>
+      </c>
+      <c r="C101">
         <v>641285173</v>
       </c>
-      <c r="C101">
-        <v>-97839258.81786178</v>
-      </c>
       <c r="D101">
-        <v>-71846566.35983987</v>
+        <v>-104701118.83400354</v>
       </c>
       <c r="E101">
+        <v>-76885454.50104539</v>
+      </c>
+      <c r="F101">
+        <v>-105824222</v>
+      </c>
+      <c r="G101">
         <v>-144456477</v>
       </c>
-      <c r="F101">
-        <v>11400606.742884627</v>
-      </c>
-      <c r="I101">
-        <v>725628.4032109573</v>
+      <c r="H101">
+        <v>12200177.06377584</v>
+      </c>
+      <c r="K101">
+        <v>776519.63630829</v>
       </c>
     </row>
     <row r="102">
@@ -4697,6 +5207,12 @@
       <c r="B104">
         <v>665619714</v>
       </c>
+      <c r="C104">
+        <v>665619714</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4712,11 +5228,11 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H107">
-        <v>2407397.6760473032</v>
-      </c>
-      <c r="I107">
-        <v>45933915.811856665</v>
+      <c r="J107">
+        <v>2576238.1400472797</v>
+      </c>
+      <c r="K107">
+        <v>49155445.73862118</v>
       </c>
     </row>
     <row r="108">
@@ -4731,20 +5247,26 @@
       <c r="B109">
         <v>0</v>
       </c>
-      <c r="D109">
-        <v>-97667844.01414223</v>
+      <c r="C109">
+        <v>0</v>
       </c>
       <c r="E109">
+        <v>-104517682.02192017</v>
+      </c>
+      <c r="F109">
+        <v>72952959</v>
+      </c>
+      <c r="G109">
         <v>19107957</v>
       </c>
-      <c r="G109">
-        <v>40917460.23421694</v>
-      </c>
-      <c r="H109">
-        <v>33462595.845617454</v>
-      </c>
       <c r="I109">
-        <v>17056297.60239604</v>
+        <v>43787165.99175878</v>
+      </c>
+      <c r="J109">
+        <v>35809462.034544826</v>
+      </c>
+      <c r="K109">
+        <v>18252524.22916531</v>
       </c>
     </row>
     <row r="110">
@@ -4752,28 +5274,34 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-73116581</v>
+      </c>
+      <c r="C110">
         <v>-47736289</v>
       </c>
-      <c r="C110">
-        <v>142679015.18447182</v>
-      </c>
       <c r="D110">
-        <v>123114793.55666691</v>
+        <v>152685667.33276132</v>
       </c>
       <c r="E110">
+        <v>131749328.29772335</v>
+      </c>
+      <c r="F110">
         <v>0</v>
       </c>
-      <c r="F110">
-        <v>65344124.949864395</v>
-      </c>
       <c r="G110">
-        <v>69634069.73362596</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>-54915715.4298739</v>
+        <v>69926970.76963861</v>
       </c>
       <c r="I110">
-        <v>-50555810.53615148</v>
+        <v>74517786.60392551</v>
+      </c>
+      <c r="J110">
+        <v>-58767175.02307839</v>
+      </c>
+      <c r="K110">
+        <v>-54101492.49545026</v>
       </c>
     </row>
     <row r="111">
@@ -4786,16 +5314,22 @@
         <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
       <c r="B112">
+        <v>-34103498</v>
+      </c>
+      <c r="C112">
         <v>-34581531</v>
       </c>
-      <c r="C112">
-        <v>-113525064.1510016</v>
-      </c>
-      <c r="E112">
+      <c r="D112">
+        <v>-121487032.66895476</v>
+      </c>
+      <c r="F112">
+        <v>-130121713</v>
+      </c>
+      <c r="G112">
         <v>-140665066</v>
       </c>
-      <c r="F112">
-        <v>-129116.91985190118</v>
+      <c r="H112">
+        <v>-138172.40780677716</v>
       </c>
     </row>
     <row r="113">
@@ -4806,13 +5340,19 @@
         <v>-384463</v>
       </c>
       <c r="C113">
-        <v>-1385860.5152154178</v>
-      </c>
-      <c r="E113">
+        <v>-384463</v>
+      </c>
+      <c r="D113">
+        <v>-1483056.4769612993</v>
+      </c>
+      <c r="F113">
+        <v>-257734</v>
+      </c>
+      <c r="G113">
         <v>-135802</v>
       </c>
-      <c r="F113">
-        <v>-488658.91398941906</v>
+      <c r="H113">
+        <v>-522930.52544630284</v>
       </c>
     </row>
     <row r="114">
@@ -4840,28 +5380,34 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-64728535</v>
+      </c>
+      <c r="C118">
         <v>-34713662</v>
       </c>
-      <c r="C118">
-        <v>-140307911.60173255</v>
-      </c>
       <c r="D118">
-        <v>-99924316.62300652</v>
+        <v>-150148268.73649567</v>
       </c>
       <c r="E118">
+        <v>-106932410.11390407</v>
+      </c>
+      <c r="F118">
+        <v>-48409373</v>
+      </c>
+      <c r="G118">
         <v>-22766821</v>
       </c>
-      <c r="F118">
-        <v>-54044743.82976035</v>
-      </c>
-      <c r="G118">
-        <v>-38243068.22746955</v>
-      </c>
       <c r="H118">
-        <v>-27964172.914582357</v>
+        <v>-57835118.68795944</v>
       </c>
       <c r="I118">
-        <v>-12475861.682165109</v>
+        <v>-40925208.136697344</v>
+      </c>
+      <c r="J118">
+        <v>-29925412.628839225</v>
+      </c>
+      <c r="K118">
+        <v>-13350843.948773766</v>
       </c>
     </row>
     <row r="119">
@@ -4869,28 +5415,34 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>173691754</v>
+      </c>
+      <c r="C119">
         <v>93081404</v>
       </c>
-      <c r="C119">
-        <v>14700562.265615974</v>
-      </c>
       <c r="D119">
-        <v>2630800.720641954</v>
+        <v>15731571.715646854</v>
       </c>
       <c r="E119">
+        <v>2815309.337055494</v>
+      </c>
+      <c r="F119">
+        <v>11639</v>
+      </c>
+      <c r="G119">
         <v>3255</v>
       </c>
-      <c r="F119">
-        <v>719001.4566219012</v>
-      </c>
-      <c r="G119">
-        <v>750260.4655650655</v>
-      </c>
       <c r="H119">
-        <v>334945.5207084776</v>
+        <v>769427.9153497427</v>
       </c>
       <c r="I119">
-        <v>767087.2072748439</v>
+        <v>802879.2440856256</v>
+      </c>
+      <c r="J119">
+        <v>358436.5947814518</v>
+      </c>
+      <c r="K119">
+        <v>820886.112745826</v>
       </c>
     </row>
     <row r="120">
@@ -4923,28 +5475,34 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-420231082</v>
+      </c>
+      <c r="C125">
         <v>-285680106</v>
       </c>
-      <c r="C125">
-        <v>594966390.2991004</v>
-      </c>
       <c r="D125">
-        <v>5774774.000386075</v>
+        <v>636693771.8621776</v>
       </c>
       <c r="E125">
+        <v>6179782.085016721</v>
+      </c>
+      <c r="F125">
+        <v>19333666</v>
+      </c>
+      <c r="G125">
         <v>-528076</v>
       </c>
-      <c r="F125">
-        <v>-20025239.32414688</v>
-      </c>
-      <c r="G125">
-        <v>-18612841.8339461</v>
-      </c>
       <c r="H125">
-        <v>-41687556.112977475</v>
+        <v>-21429689.753272038</v>
       </c>
       <c r="I125">
-        <v>-74962767.99408413</v>
+        <v>-19918235.156731665</v>
+      </c>
+      <c r="J125">
+        <v>-44611271.78620049</v>
+      </c>
+      <c r="K125">
+        <v>-80220207.86651303</v>
       </c>
     </row>
     <row r="126">
@@ -4957,28 +5515,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-420231082</v>
+      </c>
+      <c r="C127">
         <v>-285680106</v>
       </c>
-      <c r="C127">
-        <v>594966390.2991004</v>
-      </c>
       <c r="D127">
-        <v>5774774.000386075</v>
+        <v>636693771.8621776</v>
       </c>
       <c r="E127">
+        <v>6179782.085016721</v>
+      </c>
+      <c r="F127">
+        <v>19333666</v>
+      </c>
+      <c r="G127">
         <v>-528076</v>
       </c>
-      <c r="F127">
-        <v>-20025239.32414688</v>
-      </c>
-      <c r="G127">
-        <v>-18612841.8339461</v>
-      </c>
       <c r="H127">
-        <v>-41687556.112977475</v>
+        <v>-21429689.753272038</v>
       </c>
       <c r="I127">
-        <v>-74962767.99408413</v>
+        <v>-19918235.156731665</v>
+      </c>
+      <c r="J127">
+        <v>-44611271.78620049</v>
+      </c>
+      <c r="K127">
+        <v>-80220207.86651303</v>
       </c>
     </row>
     <row r="128">
@@ -4989,13 +5553,19 @@
         <v>542134587</v>
       </c>
       <c r="C128">
-        <v>1610458.8547897332</v>
-      </c>
-      <c r="E128">
+        <v>542134587</v>
+      </c>
+      <c r="D128">
+        <v>1723406.7997848527</v>
+      </c>
+      <c r="F128">
         <v>1463492</v>
       </c>
-      <c r="F128">
-        <v>21635698.178936616</v>
+      <c r="G128">
+        <v>1463492</v>
+      </c>
+      <c r="H128">
+        <v>23153096.553056892</v>
       </c>
     </row>
     <row r="129">
@@ -5003,28 +5573,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>121903505</v>
+      </c>
+      <c r="C129">
         <v>256454481</v>
       </c>
-      <c r="C129">
-        <v>596576849.1538901</v>
-      </c>
-      <c r="E129">
+      <c r="D129">
+        <v>638417178.6619625</v>
+      </c>
+      <c r="F129">
+        <v>20797158</v>
+      </c>
+      <c r="G129">
         <v>935416</v>
       </c>
-      <c r="F129">
-        <v>1610458.8547897332</v>
+      <c r="H129">
+        <v>1723406.7997848527</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5035,6 +5611,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5042,27 +5620,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5076,16 +5660,22 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>433506935</v>
+      </c>
+      <c r="C3">
         <v>-916243797</v>
       </c>
-      <c r="C3">
-        <v>616291301.0264783</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>659514284.1919798</v>
+      </c>
+      <c r="F3">
+        <v>-18178635</v>
+      </c>
+      <c r="G3">
         <v>146038809</v>
       </c>
-      <c r="F3">
-        <v>63333838.62013509</v>
+      <c r="H3">
+        <v>67775694.98890942</v>
       </c>
     </row>
     <row r="4">
@@ -5093,16 +5683,22 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>-61830292</v>
+      </c>
+      <c r="C4">
         <v>8309193</v>
       </c>
-      <c r="C4">
-        <v>20426873.117919832</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
+        <v>21859491.73744136</v>
+      </c>
+      <c r="F4">
+        <v>-37407294</v>
+      </c>
+      <c r="G4">
         <v>-67035968</v>
       </c>
-      <c r="F4">
-        <v>17941820.595849052</v>
+      <c r="H4">
+        <v>19200152.505258095</v>
       </c>
     </row>
     <row r="5">
@@ -5110,16 +5706,22 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>9113050</v>
+      </c>
+      <c r="C5">
         <v>-23946736</v>
       </c>
-      <c r="C5">
-        <v>66319557.462202966</v>
-      </c>
-      <c r="E5">
+      <c r="D5">
+        <v>70970814.28013614</v>
+      </c>
+      <c r="F5">
+        <v>59147455</v>
+      </c>
+      <c r="G5">
         <v>40038584</v>
       </c>
-      <c r="F5">
-        <v>34583003.57528931</v>
+      <c r="H5">
+        <v>37008448.45639916</v>
       </c>
     </row>
     <row r="6">
@@ -5127,26 +5729,32 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>11397888</v>
+      </c>
+      <c r="C6">
         <v>10734557</v>
       </c>
-      <c r="C6">
-        <v>10922961.337121334</v>
-      </c>
-      <c r="E6">
+      <c r="D6">
+        <v>11689032.46810349</v>
+      </c>
+      <c r="F6">
+        <v>9323910</v>
+      </c>
+      <c r="G6">
         <v>8618763</v>
       </c>
-      <c r="F6">
-        <v>7608352.028975993</v>
+      <c r="H6">
+        <v>8141956.302016847</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>0</v>
       </c>
     </row>
@@ -5155,16 +5763,22 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>1407155</v>
+      </c>
+      <c r="C8">
         <v>-873941</v>
       </c>
-      <c r="C8">
-        <v>1416736.4379844284</v>
-      </c>
-      <c r="E8">
+      <c r="D8">
+        <v>1516097.8521516589</v>
+      </c>
+      <c r="F8">
+        <v>-19207</v>
+      </c>
+      <c r="G8">
         <v>301232</v>
       </c>
-      <c r="F8">
-        <v>403535.0457448381</v>
+      <c r="H8">
+        <v>431836.5785749593</v>
       </c>
     </row>
     <row r="9">
@@ -5187,16 +5801,22 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>-50513090</v>
+      </c>
+      <c r="C12">
         <v>-58804925</v>
       </c>
-      <c r="C12">
-        <v>32020852.721114382</v>
-      </c>
-      <c r="E12">
+      <c r="D12">
+        <v>34266603.67655462</v>
+      </c>
+      <c r="F12">
+        <v>31251349</v>
+      </c>
+      <c r="G12">
         <v>23816471</v>
       </c>
-      <c r="F12">
-        <v>27209021.719901644</v>
+      <c r="H12">
+        <v>29117299.649170265</v>
       </c>
     </row>
     <row r="13">
@@ -5214,16 +5834,22 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>42079104</v>
+      </c>
+      <c r="C15">
         <v>2253377</v>
       </c>
-      <c r="C15">
-        <v>6692188.239589341</v>
-      </c>
-      <c r="E15">
+      <c r="D15">
+        <v>7161538.267958004</v>
+      </c>
+      <c r="F15">
+        <v>3335920</v>
+      </c>
+      <c r="G15">
         <v>5238464</v>
       </c>
-      <c r="F15">
-        <v>-2954474.0675966702</v>
+      <c r="H15">
+        <v>-3161683.195283441</v>
       </c>
     </row>
     <row r="16">
@@ -5251,16 +5877,22 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>4741993</v>
+      </c>
+      <c r="C20">
         <v>22744196</v>
       </c>
-      <c r="C20">
-        <v>13503823.769858377</v>
-      </c>
-      <c r="E20">
+      <c r="D20">
+        <v>14450901.14463607</v>
+      </c>
+      <c r="F20">
+        <v>15255483</v>
+      </c>
+      <c r="G20">
         <v>2063654</v>
       </c>
-      <c r="F20">
-        <v>27210669.513211273</v>
+      <c r="H20">
+        <v>29119063.00884009</v>
       </c>
     </row>
     <row r="21">
@@ -5303,26 +5935,32 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>486224177</v>
+      </c>
+      <c r="C28">
         <v>-900606254</v>
       </c>
-      <c r="C28">
-        <v>530168121.9802769</v>
-      </c>
-      <c r="E28">
+      <c r="D28">
+        <v>567350940.8405653</v>
+      </c>
+      <c r="F28">
+        <v>-39918796</v>
+      </c>
+      <c r="G28">
         <v>173036193</v>
       </c>
-      <c r="F28">
-        <v>11238499.268110693</v>
+      <c r="H28">
+        <v>12026700.340983182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>-534129977</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0</v>
       </c>
     </row>
@@ -5336,16 +5974,22 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>31334309</v>
+      </c>
+      <c r="C31">
         <v>-181447862</v>
       </c>
-      <c r="C31">
-        <v>455388387.0440779</v>
-      </c>
-      <c r="E31">
+      <c r="D31">
+        <v>487326602.8751096</v>
+      </c>
+      <c r="F31">
+        <v>-65646566</v>
+      </c>
+      <c r="G31">
         <v>181421803</v>
       </c>
-      <c r="F31">
-        <v>4224309.324052244</v>
+      <c r="H31">
+        <v>4520577.096281484</v>
       </c>
     </row>
     <row r="32">
@@ -5358,16 +6002,22 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-39903</v>
+      </c>
+      <c r="C33">
         <v>-2852763</v>
       </c>
-      <c r="C33">
-        <v>-161052.3974393677</v>
-      </c>
-      <c r="E33">
+      <c r="D33">
+        <v>-172347.64864880568</v>
+      </c>
+      <c r="F33">
+        <v>-4164</v>
+      </c>
+      <c r="G33">
         <v>-32999</v>
       </c>
-      <c r="F33">
-        <v>-140117.14070132095</v>
+      <c r="H33">
+        <v>-149944.1183069502</v>
       </c>
     </row>
     <row r="34">
@@ -5390,16 +6040,22 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-33545906</v>
+      </c>
+      <c r="C37">
         <v>-22729342</v>
       </c>
-      <c r="C37">
-        <v>4629966.359272867</v>
-      </c>
-      <c r="E37">
+      <c r="D37">
+        <v>4954684.487973325</v>
+      </c>
+      <c r="F37">
+        <v>1526051</v>
+      </c>
+      <c r="G37">
         <v>-6696267</v>
       </c>
-      <c r="F37">
-        <v>-4325161.334960996</v>
+      <c r="H37">
+        <v>-4628502.263605817</v>
       </c>
     </row>
     <row r="38">
@@ -5412,16 +6068,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>-11450146</v>
+      </c>
+      <c r="C39">
         <v>25698615</v>
       </c>
-      <c r="C39">
-        <v>-33185618.776186492</v>
-      </c>
-      <c r="E39">
+      <c r="D39">
+        <v>-35513059.451254904</v>
+      </c>
+      <c r="F39">
+        <v>2938994</v>
+      </c>
+      <c r="G39">
         <v>-3798597</v>
       </c>
-      <c r="F39">
-        <v>3946760.337822824</v>
+      <c r="H39">
+        <v>4223562.485371967</v>
       </c>
     </row>
     <row r="40">
@@ -5429,16 +6091,22 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>-16118458</v>
+      </c>
+      <c r="C40">
         <v>4238670</v>
       </c>
-      <c r="C40">
-        <v>-1184775.2293989118</v>
-      </c>
-      <c r="E40">
+      <c r="D40">
+        <v>-1267868.2727534412</v>
+      </c>
+      <c r="F40">
+        <v>17553975</v>
+      </c>
+      <c r="G40">
         <v>7777794</v>
       </c>
-      <c r="F40">
-        <v>3376357.1419544537</v>
+      <c r="H40">
+        <v>3613154.6233797967</v>
       </c>
     </row>
     <row r="41">
@@ -5451,16 +6119,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
+        <v>-944125</v>
+      </c>
+      <c r="C42">
         <v>1527322</v>
       </c>
-      <c r="C42">
-        <v>-5815447.622257123</v>
-      </c>
-      <c r="E42">
+      <c r="D42">
+        <v>-6223308.311281963</v>
+      </c>
+      <c r="F42">
+        <v>770121</v>
+      </c>
+      <c r="G42">
         <v>1898493</v>
       </c>
-      <c r="F42">
-        <v>-746336.0743586075</v>
+      <c r="H42">
+        <v>-798679.6195686064</v>
       </c>
     </row>
     <row r="43">
@@ -5473,16 +6147,22 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>-1735998</v>
+      </c>
+      <c r="C44">
         <v>-92439508</v>
       </c>
-      <c r="C44">
-        <v>115003990.19398573</v>
-      </c>
-      <c r="E44">
+      <c r="D44">
+        <v>123069681.73277734</v>
+      </c>
+      <c r="F44">
+        <v>1758142</v>
+      </c>
+      <c r="G44">
         <v>-5414744</v>
       </c>
-      <c r="F44">
-        <v>8666859.52117036</v>
+      <c r="H44">
+        <v>9274701.174228542</v>
       </c>
     </row>
     <row r="45">
@@ -5500,16 +6180,22 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>-259280</v>
+      </c>
+      <c r="C47">
         <v>257028</v>
       </c>
-      <c r="C47">
-        <v>273378.0395104422</v>
-      </c>
-      <c r="E47">
+      <c r="D47">
+        <v>292551.1389520485</v>
+      </c>
+      <c r="F47">
+        <v>-692400</v>
+      </c>
+      <c r="G47">
         <v>1136</v>
       </c>
-      <c r="F47">
-        <v>70493.02805600269</v>
+      <c r="H47">
+        <v>75436.98712191026</v>
       </c>
     </row>
     <row r="48">
@@ -5517,16 +6203,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
+        <v>-15146293</v>
+      </c>
+      <c r="C48">
         <v>-98728437</v>
       </c>
-      <c r="C48">
-        <v>-4780705.631288154</v>
-      </c>
-      <c r="E48">
+      <c r="D48">
+        <v>-5115995.710307959</v>
+      </c>
+      <c r="F48">
+        <v>1877051</v>
+      </c>
+      <c r="G48">
         <v>-2120426</v>
       </c>
-      <c r="F48">
-        <v>-3834665.534924253</v>
+      <c r="H48">
+        <v>-4103606.023919145</v>
       </c>
     </row>
     <row r="49">
@@ -5534,9 +6226,15 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>433506935</v>
+      </c>
+      <c r="C49">
         <v>-916243797</v>
       </c>
-      <c r="E49">
+      <c r="F49">
+        <v>-18178635</v>
+      </c>
+      <c r="G49">
         <v>146038809</v>
       </c>
     </row>
@@ -5626,16 +6324,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-593751129</v>
+      </c>
+      <c r="C67">
         <v>-10721482</v>
       </c>
-      <c r="C67">
-        <v>-1106992.269742054</v>
-      </c>
-      <c r="E67">
+      <c r="D67">
+        <v>-1184630.0818606215</v>
+      </c>
+      <c r="F67">
+        <v>-591878</v>
+      </c>
+      <c r="G67">
         <v>-2110408</v>
       </c>
-      <c r="F67">
-        <v>-13117244.551202802</v>
+      <c r="H67">
+        <v>-14037209.5733767</v>
       </c>
     </row>
     <row r="68">
@@ -5687,10 +6391,10 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>0</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>0</v>
       </c>
     </row>
@@ -5699,16 +6403,22 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
         <v>-10721482</v>
       </c>
-      <c r="C78">
-        <v>-1106992.269742054</v>
-      </c>
-      <c r="E78">
+      <c r="D78">
+        <v>-1184630.0818606215</v>
+      </c>
+      <c r="F78">
+        <v>-591878</v>
+      </c>
+      <c r="G78">
         <v>-2110408</v>
       </c>
-      <c r="F78">
-        <v>-13117244.551202802</v>
+      <c r="H78">
+        <v>-14037209.5733767</v>
       </c>
     </row>
     <row r="79">
@@ -5790,10 +6500,10 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="B94">
+      <c r="C94">
         <v>0</v>
       </c>
-      <c r="E94">
+      <c r="G94">
         <v>0</v>
       </c>
     </row>
@@ -5828,12 +6538,18 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>25693218</v>
+      </c>
+      <c r="C101">
         <v>641285173</v>
       </c>
-      <c r="C101">
-        <v>-25992692.45802191</v>
-      </c>
-      <c r="E101">
+      <c r="D101">
+        <v>-27815664.332958147</v>
+      </c>
+      <c r="F101">
+        <v>38632255</v>
+      </c>
+      <c r="G101">
         <v>-144456477</v>
       </c>
     </row>
@@ -5852,6 +6568,9 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
         <v>665619714</v>
       </c>
     </row>
@@ -5882,7 +6601,13 @@
       <c r="B109">
         <v>0</v>
       </c>
-      <c r="E109">
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>53845002</v>
+      </c>
+      <c r="G109">
         <v>19107957</v>
       </c>
     </row>
@@ -5891,16 +6616,22 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-25380292</v>
+      </c>
+      <c r="C110">
         <v>-47736289</v>
       </c>
-      <c r="C110">
-        <v>19564221.627804905</v>
-      </c>
-      <c r="E110">
+      <c r="D110">
+        <v>20936339.035037965</v>
+      </c>
+      <c r="F110">
         <v>0</v>
       </c>
-      <c r="F110">
-        <v>-4289944.783761568</v>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>-4590815.834286898</v>
       </c>
     </row>
     <row r="111">
@@ -5913,9 +6644,15 @@
         <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
       <c r="B112">
+        <v>478033</v>
+      </c>
+      <c r="C112">
         <v>-34581531</v>
       </c>
-      <c r="E112">
+      <c r="F112">
+        <v>10543353</v>
+      </c>
+      <c r="G112">
         <v>-140665066</v>
       </c>
     </row>
@@ -5924,9 +6661,15 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
         <v>-384463</v>
       </c>
-      <c r="E113">
+      <c r="F113">
+        <v>-121932</v>
+      </c>
+      <c r="G113">
         <v>-135802</v>
       </c>
     </row>
@@ -5955,16 +6698,22 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-30014873</v>
+      </c>
+      <c r="C118">
         <v>-34713662</v>
       </c>
-      <c r="C118">
-        <v>-40383594.97872603</v>
-      </c>
-      <c r="E118">
+      <c r="D118">
+        <v>-43215858.6225916</v>
+      </c>
+      <c r="F118">
+        <v>-25642552</v>
+      </c>
+      <c r="G118">
         <v>-22766821</v>
       </c>
-      <c r="F118">
-        <v>-15801675.602290802</v>
+      <c r="H118">
+        <v>-16909910.551262096</v>
       </c>
     </row>
     <row r="119">
@@ -5972,16 +6721,22 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
+        <v>80610350</v>
+      </c>
+      <c r="C119">
         <v>93081404</v>
       </c>
-      <c r="C119">
-        <v>12069761.54497402</v>
-      </c>
-      <c r="E119">
+      <c r="D119">
+        <v>12916262.378591359</v>
+      </c>
+      <c r="F119">
+        <v>8384</v>
+      </c>
+      <c r="G119">
         <v>3255</v>
       </c>
-      <c r="F119">
-        <v>-31259.008943164255</v>
+      <c r="H119">
+        <v>-33451.32873588288</v>
       </c>
     </row>
     <row r="120">
@@ -6014,16 +6769,22 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-134550976</v>
+      </c>
+      <c r="C125">
         <v>-285680106</v>
       </c>
-      <c r="C125">
-        <v>589191616.2987143</v>
-      </c>
-      <c r="E125">
+      <c r="D125">
+        <v>630513989.7771609</v>
+      </c>
+      <c r="F125">
+        <v>19861742</v>
+      </c>
+      <c r="G125">
         <v>-528076</v>
       </c>
-      <c r="F125">
-        <v>-1412397.4902007803</v>
+      <c r="H125">
+        <v>-1511454.5965403728</v>
       </c>
     </row>
     <row r="126">
@@ -6036,16 +6797,22 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-134550976</v>
+      </c>
+      <c r="C127">
         <v>-285680106</v>
       </c>
-      <c r="C127">
-        <v>589191616.2987143</v>
-      </c>
-      <c r="E127">
+      <c r="D127">
+        <v>630513989.7771609</v>
+      </c>
+      <c r="F127">
+        <v>19861742</v>
+      </c>
+      <c r="G127">
         <v>-528076</v>
       </c>
-      <c r="F127">
-        <v>-1412397.4902007803</v>
+      <c r="H127">
+        <v>-1511454.5965403728</v>
       </c>
     </row>
     <row r="128">
@@ -6053,9 +6820,15 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
         <v>542134587</v>
       </c>
-      <c r="E128">
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
         <v>1463492</v>
       </c>
     </row>
@@ -6064,22 +6837,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>-134550976</v>
+      </c>
+      <c r="C129">
         <v>256454481</v>
       </c>
-      <c r="E129">
+      <c r="F129">
+        <v>19861742</v>
+      </c>
+      <c r="G129">
         <v>935416</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6090,6 +6869,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6097,27 +6878,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6130,80 +6917,80 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
-      <c r="C3">
-        <v>698880825.0122173</v>
-      </c>
       <c r="D3">
-        <v>145923362.60587406</v>
-      </c>
-      <c r="F3">
-        <v>-23323163.467789076</v>
+        <v>747896143.0669775</v>
+      </c>
+      <c r="E3">
+        <v>156157553.86390722</v>
       </c>
       <c r="H3">
-        <v>19466689.021406382</v>
-      </c>
-      <c r="I3">
-        <v>-47683820.01036463</v>
+        <v>-24958910.557283</v>
+      </c>
+      <c r="J3">
+        <v>20831966.075388603</v>
+      </c>
+      <c r="K3">
+        <v>-51028077.74391041</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
-      <c r="C4">
-        <v>-133662191.08709201</v>
-      </c>
       <c r="D4">
-        <v>-136147243.6091628</v>
-      </c>
-      <c r="F4">
-        <v>8768421.4281974</v>
+        <v>-143036457.16159108</v>
+      </c>
+      <c r="E4">
+        <v>-145695796.39377436</v>
       </c>
       <c r="H4">
-        <v>116205577.00564857</v>
-      </c>
-      <c r="I4">
-        <v>5749517.236776926</v>
+        <v>9383386.025535949</v>
+      </c>
+      <c r="J4">
+        <v>124355540.65155233</v>
+      </c>
+      <c r="K4">
+        <v>6152753.96317734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C5">
-        <v>209810106.68462977</v>
-      </c>
       <c r="D5">
-        <v>178073552.7977161</v>
-      </c>
-      <c r="F5">
-        <v>59780611.19096039</v>
+        <v>224524931.7909997</v>
+      </c>
+      <c r="E5">
+        <v>190562565.96726274</v>
       </c>
       <c r="H5">
-        <v>134767612.48366308</v>
-      </c>
-      <c r="I5">
-        <v>34066912.777169295</v>
+        <v>63973265.45498554</v>
+      </c>
+      <c r="J5">
+        <v>144219406.19863865</v>
+      </c>
+      <c r="K5">
+        <v>36456162.13865741</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C6">
-        <v>42939214.156960845</v>
-      </c>
       <c r="D6">
-        <v>39624604.8488155</v>
-      </c>
-      <c r="F6">
-        <v>41219091.64317405</v>
+        <v>45950713.63383962</v>
+      </c>
+      <c r="E6">
+        <v>42403637.46775298</v>
       </c>
       <c r="H6">
-        <v>20612617.34768741</v>
-      </c>
-      <c r="I6">
-        <v>12490219.4759</v>
+        <v>44109952.02238558</v>
+      </c>
+      <c r="J6">
+        <v>22058262.955749847</v>
+      </c>
+      <c r="K6">
+        <v>13366208.712225517</v>
       </c>
     </row>
     <row r="7">
@@ -6215,20 +7002,20 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C8">
-        <v>1746134.2900107289</v>
-      </c>
       <c r="D8">
-        <v>732932.8977711387</v>
-      </c>
-      <c r="F8">
-        <v>1261960.6962636637</v>
+        <v>1868597.6979740288</v>
+      </c>
+      <c r="E8">
+        <v>784336.4243973291</v>
       </c>
       <c r="H8">
-        <v>203693.94966767836</v>
-      </c>
-      <c r="I8">
-        <v>79255.52668967278</v>
+        <v>1350467.06628589</v>
+      </c>
+      <c r="J8">
+        <v>217979.8241279156</v>
+      </c>
+      <c r="K8">
+        <v>84814.03496356045</v>
       </c>
     </row>
     <row r="9">
@@ -6250,20 +7037,20 @@
       <c r="A12" t="str">
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C12">
-        <v>117079859.81185986</v>
-      </c>
       <c r="D12">
-        <v>112268028.81064713</v>
-      </c>
-      <c r="F12">
-        <v>50697639.62422628</v>
+        <v>125291140.42094615</v>
+      </c>
+      <c r="E12">
+        <v>120141836.3935618</v>
       </c>
       <c r="H12">
-        <v>27629227.393873878</v>
-      </c>
-      <c r="I12">
-        <v>11708774.474890266</v>
+        <v>54253268.62687294</v>
+      </c>
+      <c r="J12">
+        <v>29566976.034057774</v>
+      </c>
+      <c r="K12">
+        <v>12529957.836027943</v>
       </c>
     </row>
     <row r="13">
@@ -6280,20 +7067,20 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C15">
-        <v>19081782.582816098</v>
-      </c>
       <c r="D15">
-        <v>9435120.275630087</v>
-      </c>
-      <c r="F15">
-        <v>13035699.645501968</v>
+        <v>20420064.60297621</v>
+      </c>
+      <c r="E15">
+        <v>10096843.139734766</v>
       </c>
       <c r="H15">
-        <v>94327624.96917932</v>
-      </c>
-      <c r="I15">
-        <v>45802046.42964819</v>
+        <v>13949945.596060755</v>
+      </c>
+      <c r="J15">
+        <v>100943200.00535755</v>
+      </c>
+      <c r="K15">
+        <v>49014327.82722246</v>
       </c>
     </row>
     <row r="16">
@@ -6310,11 +7097,11 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>1762994.9565351023</v>
-      </c>
-      <c r="F18">
-        <v>-24894100.664947763</v>
+      <c r="D18">
+        <v>1886640.8707322697</v>
+      </c>
+      <c r="H18">
+        <v>-26640023.886919554</v>
       </c>
     </row>
     <row r="19">
@@ -6326,20 +7113,20 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C20">
-        <v>27200120.886447135</v>
-      </c>
       <c r="D20">
-        <v>40906966.62980003</v>
-      </c>
-      <c r="F20">
-        <v>-21539679.753257804</v>
+        <v>29107774.564531416</v>
+      </c>
+      <c r="E20">
+        <v>43775936.428735435</v>
       </c>
       <c r="H20">
-        <v>43878646.38607516</v>
-      </c>
-      <c r="I20">
-        <v>27195192.081628166</v>
+        <v>-23050343.969700076</v>
+      </c>
+      <c r="J20">
+        <v>46956032.016720034</v>
+      </c>
+      <c r="K20">
+        <v>29102500.082842823</v>
       </c>
     </row>
     <row r="21">
@@ -6356,11 +7143,11 @@
       <c r="A23" t="str">
         <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="H23">
-        <v>-26621147.897292126</v>
-      </c>
-      <c r="I23">
-        <v>-681371.0753262334</v>
+      <c r="J23">
+        <v>-28488195.875244267</v>
+      </c>
+      <c r="K23">
+        <v>-729158.3643391284</v>
       </c>
     </row>
     <row r="24">
@@ -6387,20 +7174,20 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
-      <c r="C28">
-        <v>623356160.9486009</v>
-      </c>
       <c r="D28">
-        <v>104426538.23643471</v>
-      </c>
-      <c r="F28">
-        <v>-91442711.2678329</v>
+        <v>667074631.103732</v>
+      </c>
+      <c r="E28">
+        <v>111750390.60414985</v>
       </c>
       <c r="H28">
-        <v>-231506500.46790525</v>
-      </c>
-      <c r="I28">
-        <v>-87500250.02431086</v>
+        <v>-97855955.72407347</v>
+      </c>
+      <c r="J28">
+        <v>-247742980.77480236</v>
+      </c>
+      <c r="K28">
+        <v>-93636993.84574518</v>
       </c>
     </row>
     <row r="29">
@@ -6417,20 +7204,20 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C31">
-        <v>558247927.9697257</v>
-      </c>
       <c r="D31">
-        <v>107083850.24970011</v>
-      </c>
-      <c r="F31">
-        <v>-122393597.57487328</v>
+        <v>597400096.3560435</v>
+      </c>
+      <c r="E31">
+        <v>114594070.57721533</v>
       </c>
       <c r="H31">
-        <v>-324571987.74884325</v>
-      </c>
-      <c r="I31">
-        <v>-121659131.68771864</v>
+        <v>-130977551.94634123</v>
+      </c>
+      <c r="J31">
+        <v>-347335524.3087384</v>
+      </c>
+      <c r="K31">
+        <v>-130191575.01786044</v>
       </c>
     </row>
     <row r="32">
@@ -6442,20 +7229,20 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C33">
-        <v>-203764.0490570226</v>
-      </c>
       <c r="D33">
-        <v>-182828.79231897587</v>
-      </c>
-      <c r="F33">
-        <v>3217404.062000017</v>
+        <v>-218054.8398688626</v>
+      </c>
+      <c r="E33">
+        <v>-195651.3095270071</v>
       </c>
       <c r="H33">
-        <v>-3134192.8007198814</v>
-      </c>
-      <c r="I33">
-        <v>-333744.34880999755</v>
+        <v>3443053.5257792696</v>
+      </c>
+      <c r="J33">
+        <v>-3354006.3246773304</v>
+      </c>
+      <c r="K33">
+        <v>-357151.1798753869</v>
       </c>
     </row>
     <row r="34">
@@ -6477,20 +7264,20 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C37">
-        <v>-10797760.33488433</v>
-      </c>
       <c r="D37">
-        <v>-19752888.029118195</v>
-      </c>
-      <c r="F37">
-        <v>6999860.536974902</v>
+        <v>-11555050.616935177</v>
+      </c>
+      <c r="E37">
+        <v>-21138237.368514318</v>
       </c>
       <c r="H37">
-        <v>-19180191.150052566</v>
-      </c>
-      <c r="I37">
-        <v>-5788299.241896876</v>
+        <v>7490788.8587711</v>
+      </c>
+      <c r="J37">
+        <v>-20525374.95811382</v>
+      </c>
+      <c r="K37">
+        <v>-6194255.906014457</v>
       </c>
     </row>
     <row r="38">
@@ -6502,40 +7289,40 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
-      <c r="C39">
-        <v>-35490427.64465959</v>
-      </c>
       <c r="D39">
-        <v>1641951.4693497214</v>
-      </c>
-      <c r="F39">
-        <v>-5159863.548065239</v>
+        <v>-37979513.81878955</v>
+      </c>
+      <c r="E39">
+        <v>1757108.1178373238</v>
       </c>
       <c r="H39">
-        <v>-250897.93825173288</v>
-      </c>
-      <c r="I39">
-        <v>-943571.0535634737</v>
+        <v>-5521745.493993803</v>
+      </c>
+      <c r="J39">
+        <v>-268494.4179412097</v>
+      </c>
+      <c r="K39">
+        <v>-1009747.479704326</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C40">
-        <v>3218464.868848307</v>
-      </c>
       <c r="D40">
-        <v>7779597.240201673</v>
-      </c>
-      <c r="F40">
-        <v>18406219.18587199</v>
+        <v>3444188.731270651</v>
+      </c>
+      <c r="E40">
+        <v>8325211.627403889</v>
       </c>
       <c r="H40">
-        <v>-4210294.684879515</v>
-      </c>
-      <c r="I40">
-        <v>10893978.005957436</v>
+        <v>19697121.232820228</v>
+      </c>
+      <c r="J40">
+        <v>-4505579.554199014</v>
+      </c>
+      <c r="K40">
+        <v>11658016.419565696</v>
       </c>
     </row>
     <row r="41">
@@ -6547,20 +7334,20 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
-      <c r="C42">
-        <v>-517580.20609185885</v>
-      </c>
       <c r="D42">
-        <v>4551531.341806657</v>
-      </c>
-      <c r="F42">
-        <v>891329.7492109839</v>
+        <v>-553880.1838741901</v>
+      </c>
+      <c r="E42">
+        <v>4870748.5078391675</v>
       </c>
       <c r="H42">
-        <v>333479.0804461841</v>
-      </c>
-      <c r="I42">
-        <v>51479.28779824306</v>
+        <v>953842.282944446</v>
+      </c>
+      <c r="J42">
+        <v>356867.3071762463</v>
+      </c>
+      <c r="K42">
+        <v>55089.736925416226</v>
       </c>
     </row>
     <row r="43">
@@ -6572,20 +7359,20 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C44">
-        <v>111695822.68712844</v>
-      </c>
       <c r="D44">
-        <v>5358692.01431307</v>
-      </c>
-      <c r="F44">
-        <v>12874858.658607177</v>
+        <v>119529499.15736498</v>
+      </c>
+      <c r="E44">
+        <v>5734518.598816183</v>
       </c>
       <c r="H44">
-        <v>123573627.44171154</v>
-      </c>
-      <c r="I44">
-        <v>29318424.180897</v>
+        <v>13777824.185026769</v>
+      </c>
+      <c r="J44">
+        <v>132240342.04520643</v>
+      </c>
+      <c r="K44">
+        <v>31374642.973372698</v>
       </c>
     </row>
     <row r="45">
@@ -6602,51 +7389,51 @@
       <c r="A47" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
-      <c r="C47">
-        <v>-1128909.7676123476</v>
-      </c>
       <c r="D47">
-        <v>-1331794.779066787</v>
-      </c>
-      <c r="F47">
-        <v>-332264.73256551893</v>
+        <v>-1208084.741848731</v>
+      </c>
+      <c r="E47">
+        <v>-1425198.8936788691</v>
       </c>
       <c r="H47">
-        <v>-2324902.659944999</v>
-      </c>
-      <c r="I47">
-        <v>2680699.881736269</v>
+        <v>-355567.79220346804</v>
+      </c>
+      <c r="J47">
+        <v>-2487957.4172730027</v>
+      </c>
+      <c r="K47">
+        <v>2868708.126647502</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C48">
-        <v>-1667612.5747964494</v>
-      </c>
       <c r="D48">
-        <v>-721572.4784325478</v>
-      </c>
-      <c r="F48">
-        <v>-5946657.6049939245</v>
+        <v>-1784568.9396306637</v>
+      </c>
+      <c r="E48">
+        <v>-772179.2532418501</v>
       </c>
       <c r="H48">
-        <v>-1741140.007371066</v>
-      </c>
-      <c r="I48">
-        <v>-1720085.048710806</v>
+        <v>-6363720.576876778</v>
+      </c>
+      <c r="J48">
+        <v>-1863253.1462423012</v>
+      </c>
+      <c r="K48">
+        <v>-1840721.5188018607</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
-      <c r="C49">
-        <v>699504076.5461386</v>
-      </c>
-      <c r="F49">
-        <v>-22893678.648675106</v>
+      <c r="D49">
+        <v>748563105.7331406</v>
+      </c>
+      <c r="H49">
+        <v>-24499304.243551984</v>
       </c>
     </row>
     <row r="50">
@@ -6673,11 +7460,11 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="H54">
-        <v>-37152.499456524965</v>
-      </c>
-      <c r="I54">
-        <v>-63977.906290649255</v>
+      <c r="J54">
+        <v>-39758.15339954028</v>
+      </c>
+      <c r="K54">
+        <v>-68464.93371089504</v>
       </c>
     </row>
     <row r="55">
@@ -6719,17 +7506,17 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-623251.533921289</v>
-      </c>
-      <c r="F62">
-        <v>-429484.81911396835</v>
+      <c r="D62">
+        <v>-666962.6661629486</v>
       </c>
       <c r="H62">
-        <v>-162754.1988524658</v>
-      </c>
-      <c r="I62">
-        <v>-54776.19460563907</v>
+        <v>-459606.31373101455</v>
+      </c>
+      <c r="J62">
+        <v>-174168.804227226</v>
+      </c>
+      <c r="K62">
+        <v>-58617.86904330576</v>
       </c>
     </row>
     <row r="63">
@@ -6752,20 +7539,20 @@
       <c r="A67" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
-      <c r="C67">
-        <v>-6075175.895255089</v>
-      </c>
       <c r="D67">
-        <v>-18085428.176715836</v>
-      </c>
-      <c r="F67">
-        <v>-8102682.599242431</v>
+        <v>-6501252.370796302</v>
+      </c>
+      <c r="E67">
+        <v>-19353831.86231238</v>
       </c>
       <c r="H67">
-        <v>-14279389.13399184</v>
-      </c>
-      <c r="I67">
-        <v>-27885822.286034174</v>
+        <v>-8670956.259764876</v>
+      </c>
+      <c r="J67">
+        <v>-15280860.021418264</v>
+      </c>
+      <c r="K67">
+        <v>-29841566.956156712</v>
       </c>
     </row>
     <row r="68">
@@ -6817,31 +7604,31 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H77">
-        <v>1411339.085233516</v>
-      </c>
-      <c r="I77">
-        <v>1062809.7572715771</v>
+      <c r="J77">
+        <v>1510321.9613835749</v>
+      </c>
+      <c r="K77">
+        <v>1137348.8724110692</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="C78">
-        <v>-6075175.895255089</v>
-      </c>
       <c r="D78">
-        <v>-18085428.176715836</v>
-      </c>
-      <c r="F78">
-        <v>-8102682.599242431</v>
+        <v>-6501252.370796302</v>
+      </c>
+      <c r="E78">
+        <v>-19353831.86231238</v>
       </c>
       <c r="H78">
-        <v>-15690728.219225354</v>
-      </c>
-      <c r="I78">
-        <v>-28948632.043305755</v>
+        <v>-8670956.259764876</v>
+      </c>
+      <c r="J78">
+        <v>-16791181.98280184</v>
+      </c>
+      <c r="K78">
+        <v>-30978915.828567784</v>
       </c>
     </row>
     <row r="79">
@@ -6943,8 +7730,8 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H98">
-        <v>-46674949.30208302</v>
+      <c r="J98">
+        <v>-49948450.88254406</v>
       </c>
     </row>
     <row r="99">
@@ -6957,14 +7744,14 @@
       <c r="A101" t="str">
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
-      <c r="C101">
-        <v>-97839258.81786178</v>
-      </c>
-      <c r="F101">
-        <v>11400606.742884627</v>
-      </c>
-      <c r="I101">
-        <v>725628.4032109573</v>
+      <c r="D101">
+        <v>-104701118.83400354</v>
+      </c>
+      <c r="H101">
+        <v>12200177.06377584</v>
+      </c>
+      <c r="K101">
+        <v>776519.63630829</v>
       </c>
     </row>
     <row r="102">
@@ -6996,11 +7783,11 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H107">
-        <v>2407397.6760473032</v>
-      </c>
-      <c r="I107">
-        <v>45933915.811856665</v>
+      <c r="J107">
+        <v>2576238.1400472797</v>
+      </c>
+      <c r="K107">
+        <v>49155445.73862118</v>
       </c>
     </row>
     <row r="108">
@@ -7012,31 +7799,31 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H109">
-        <v>33462595.845617454</v>
-      </c>
-      <c r="I109">
-        <v>17056297.60239604</v>
+      <c r="J109">
+        <v>35809462.034544826</v>
+      </c>
+      <c r="K109">
+        <v>18252524.22916531</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="C110">
-        <v>142679015.18447182</v>
-      </c>
       <c r="D110">
-        <v>118824848.77290535</v>
-      </c>
-      <c r="F110">
-        <v>65344124.949864395</v>
+        <v>152685667.33276132</v>
+      </c>
+      <c r="E110">
+        <v>127158512.46343645</v>
       </c>
       <c r="H110">
-        <v>-54915715.4298739</v>
-      </c>
-      <c r="I110">
-        <v>-50555810.53615148</v>
+        <v>69926970.76963861</v>
+      </c>
+      <c r="J110">
+        <v>-58767175.02307839</v>
+      </c>
+      <c r="K110">
+        <v>-54101492.49545026</v>
       </c>
     </row>
     <row r="111">
@@ -7048,22 +7835,22 @@
       <c r="A112" t="str">
         <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
-      <c r="C112">
-        <v>-113525064.1510016</v>
-      </c>
-      <c r="F112">
-        <v>-129116.91985190118</v>
+      <c r="D112">
+        <v>-121487032.66895476</v>
+      </c>
+      <c r="H112">
+        <v>-138172.40780677716</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="C113">
-        <v>-1385860.5152154178</v>
-      </c>
-      <c r="F113">
-        <v>-488658.91398941906</v>
+      <c r="D113">
+        <v>-1483056.4769612993</v>
+      </c>
+      <c r="H113">
+        <v>-522930.52544630284</v>
       </c>
     </row>
     <row r="114">
@@ -7090,40 +7877,40 @@
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
-      <c r="C118">
-        <v>-140307911.60173255</v>
-      </c>
       <c r="D118">
-        <v>-115725992.22529733</v>
-      </c>
-      <c r="F118">
-        <v>-54044743.82976035</v>
+        <v>-150148268.73649567</v>
+      </c>
+      <c r="E118">
+        <v>-123842320.66516617</v>
       </c>
       <c r="H118">
-        <v>-27964172.914582357</v>
-      </c>
-      <c r="I118">
-        <v>-12475861.682165109</v>
+        <v>-57835118.68795944</v>
+      </c>
+      <c r="J118">
+        <v>-29925412.628839225</v>
+      </c>
+      <c r="K118">
+        <v>-13350843.948773766</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="C119">
-        <v>14700562.265615974</v>
-      </c>
       <c r="D119">
-        <v>2599541.7116987896</v>
-      </c>
-      <c r="F119">
-        <v>719001.4566219012</v>
+        <v>15731571.715646854</v>
+      </c>
+      <c r="E119">
+        <v>2781858.008319611</v>
       </c>
       <c r="H119">
-        <v>334945.5207084776</v>
-      </c>
-      <c r="I119">
-        <v>767087.2072748439</v>
+        <v>769427.9153497427</v>
+      </c>
+      <c r="J119">
+        <v>358436.5947814518</v>
+      </c>
+      <c r="K119">
+        <v>820886.112745826</v>
       </c>
     </row>
     <row r="120">
@@ -7155,20 +7942,20 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
-      <c r="C125">
-        <v>594966390.2991004</v>
-      </c>
       <c r="D125">
-        <v>4362376.510185295</v>
-      </c>
-      <c r="F125">
-        <v>-20025239.32414688</v>
+        <v>636693771.8621776</v>
+      </c>
+      <c r="E125">
+        <v>4668327.488476348</v>
       </c>
       <c r="H125">
-        <v>-41687556.112977475</v>
-      </c>
-      <c r="I125">
-        <v>-74962767.99408413</v>
+        <v>-21429689.753272038</v>
+      </c>
+      <c r="J125">
+        <v>-44611271.78620049</v>
+      </c>
+      <c r="K125">
+        <v>-80220207.86651303</v>
       </c>
     </row>
     <row r="126">
@@ -7180,47 +7967,47 @@
       <c r="A127" t="str">
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
-      <c r="C127">
-        <v>594966390.2991004</v>
-      </c>
       <c r="D127">
-        <v>4362376.510185295</v>
-      </c>
-      <c r="F127">
-        <v>-20025239.32414688</v>
+        <v>636693771.8621776</v>
+      </c>
+      <c r="E127">
+        <v>4668327.488476348</v>
       </c>
       <c r="H127">
-        <v>-41687556.112977475</v>
-      </c>
-      <c r="I127">
-        <v>-74962767.99408413</v>
+        <v>-21429689.753272038</v>
+      </c>
+      <c r="J127">
+        <v>-44611271.78620049</v>
+      </c>
+      <c r="K127">
+        <v>-80220207.86651303</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
-      <c r="C128">
-        <v>1610458.8547897332</v>
-      </c>
-      <c r="F128">
-        <v>21635698.178936616</v>
+      <c r="D128">
+        <v>1723406.7997848527</v>
+      </c>
+      <c r="H128">
+        <v>23153096.553056892</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
-      <c r="C129">
-        <v>596576849.1538901</v>
-      </c>
-      <c r="F129">
-        <v>1610458.8547897332</v>
+      <c r="D129">
+        <v>638417178.6619625</v>
+      </c>
+      <c r="H129">
+        <v>1723406.7997848527</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>